--- a/events/LeeValley_2015_WCH/LeeValley_2015_WCH_start.xlsx
+++ b/events/LeeValley_2015_WCH/LeeValley_2015_WCH_start.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W845"/>
+  <dimension ref="A1:AC845"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,17 +519,47 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Name4</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Name5</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Name6</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
           <t>ICF_ID1</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>ICF_ID2</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>ICF_ID3</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ICF_ID4</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ICF_ID5</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>ICF_ID6</t>
         </is>
       </c>
     </row>
@@ -1217,12 +1247,12 @@
           <t>SHAMSIBOEV Shoxruxmirzo</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>67344</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>67346</t>
         </is>
@@ -1285,7 +1315,7 @@
           <t>ZINOVYEV Pavel</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>39682</t>
         </is>
@@ -1348,12 +1378,12 @@
           <t>ERGASHEV Muhibillo</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>61155</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>61161</t>
         </is>
@@ -1532,12 +1562,12 @@
           <t>DENNIS Tad</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>51904</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>42253</t>
         </is>
@@ -1600,12 +1630,12 @@
           <t>ROSSI Sebastian</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>36925</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>36915</t>
         </is>
@@ -1668,12 +1698,12 @@
           <t>SMEDLEY Cameron</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>35539</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>35543</t>
         </is>
@@ -1736,12 +1766,12 @@
           <t>CHEN Jin</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>42237</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>42238</t>
         </is>
@@ -1804,12 +1834,12 @@
           <t>SILVA Jose</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>41649</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>36494</t>
         </is>
@@ -1872,12 +1902,12 @@
           <t>DE SOUZA Rafael</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>60498</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>38021</t>
         </is>
@@ -1940,12 +1970,12 @@
           <t>DENG Xiao</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>42239</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>42240</t>
         </is>
@@ -2008,7 +2038,7 @@
           <t>SASAKI Tsubasa</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>41610</t>
         </is>
@@ -2071,12 +2101,12 @@
           <t>OLIVEIRA Anderson</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>38018</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>38020</t>
         </is>
@@ -2139,12 +2169,12 @@
           <t>OBRAZTSOV Maxim</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>35770</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>35767</t>
         </is>
@@ -2207,12 +2237,12 @@
           <t>HUANG Yongze</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>52028</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>52029</t>
         </is>
@@ -2275,12 +2305,12 @@
           <t>WERRO Simon</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>35424</t>
         </is>
@@ -2343,12 +2373,12 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>35068</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -2411,7 +2441,7 @@
           <t>PITT Greg</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -2474,12 +2504,12 @@
           <t>USHAKOV Artem</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>35454</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>35455</t>
         </is>
@@ -2542,12 +2572,12 @@
           <t>KERVELLA Loic</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>35671</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>35672</t>
         </is>
@@ -2610,12 +2640,12 @@
           <t>FERRARI Niccolo</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>35497</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
+      <c r="Y37" t="inlineStr">
         <is>
           <t>35498</t>
         </is>
@@ -2678,12 +2708,12 @@
           <t>VRZAN Jakub</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>35042</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="Y38" t="inlineStr">
         <is>
           <t>35043</t>
         </is>
@@ -2746,12 +2776,12 @@
           <t>LARIONOV Dmitry</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>35449</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
+      <c r="Y39" t="inlineStr">
         <is>
           <t>35450</t>
         </is>
@@ -2814,12 +2844,12 @@
           <t>PEREZ Jesus</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>35757</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr">
+      <c r="Y40" t="inlineStr">
         <is>
           <t>36091</t>
         </is>
@@ -2882,7 +2912,7 @@
           <t>Lee Valley, London</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>35356</t>
         </is>
@@ -2945,12 +2975,12 @@
           <t>MAJERCZAK Grzegorz</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>35085</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="Y42" t="inlineStr">
         <is>
           <t>35086</t>
         </is>
@@ -3013,12 +3043,12 @@
           <t>MUELLER Kevin</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>35148</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="Y43" t="inlineStr">
         <is>
           <t>35149</t>
         </is>
@@ -3081,12 +3111,12 @@
           <t>BRZEZINSKI Andrzej</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>35082</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="Y44" t="inlineStr">
         <is>
           <t>35081</t>
         </is>
@@ -3149,12 +3179,12 @@
           <t>BATIK Jan</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>35368</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="Y45" t="inlineStr">
         <is>
           <t>35367</t>
         </is>
@@ -3217,12 +3247,12 @@
           <t>BENZIEN Jan</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr">
+      <c r="Y46" t="inlineStr">
         <is>
           <t>35134</t>
         </is>
@@ -3285,12 +3315,12 @@
           <t>POCHWALA Marcin</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>35080</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr">
+      <c r="Y47" t="inlineStr">
         <is>
           <t>35079</t>
         </is>
@@ -3353,12 +3383,12 @@
           <t>BECKER Thomas</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>35139</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="Y48" t="inlineStr">
         <is>
           <t>35143</t>
         </is>
@@ -3421,12 +3451,12 @@
           <t>BISO Hugo</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>35403</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr">
+      <c r="Y49" t="inlineStr">
         <is>
           <t>35229</t>
         </is>
@@ -3489,12 +3519,12 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>35060</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
+      <c r="Y50" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
@@ -3557,7 +3587,7 @@
           <t>HOUNSLOW Richard</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -3620,12 +3650,12 @@
           <t>SINDLER Marek</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>35062</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr">
+      <c r="Y52" t="inlineStr">
         <is>
           <t>35063</t>
         </is>
@@ -3688,12 +3718,12 @@
           <t>TALJAT Saso</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr">
+      <c r="Y53" t="inlineStr">
         <is>
           <t>36270</t>
         </is>
@@ -3756,12 +3786,12 @@
           <t>SKANTAR Peter</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>35360</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr">
+      <c r="Y54" t="inlineStr">
         <is>
           <t>35361</t>
         </is>
@@ -3824,12 +3854,12 @@
           <t>PECHE Matthieu</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>35350</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr">
+      <c r="Y55" t="inlineStr">
         <is>
           <t>35400</t>
         </is>
@@ -3887,7 +3917,7 @@
           <t>BEYAZOGLU Buse</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>61581</t>
         </is>
@@ -3998,7 +4028,7 @@
           <t>SAMLAL Jihane</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>38424</t>
         </is>
@@ -4056,7 +4086,7 @@
           <t>XU Yanru</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>63801</t>
         </is>
@@ -4114,7 +4144,7 @@
           <t>SMIRNOVA Yekaterina</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>38002</t>
         </is>
@@ -4172,7 +4202,7 @@
           <t>SAETHER Mariann</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>53420</t>
         </is>
@@ -4230,7 +4260,7 @@
           <t>BARANAUSKAITE Erika</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>35622</t>
         </is>
@@ -4288,7 +4318,7 @@
           <t>JAMILI Hind</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>43390</t>
         </is>
@@ -4399,7 +4429,7 @@
           <t>REINOSO Sofia</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>45745</t>
         </is>
@@ -4457,7 +4487,7 @@
           <t>JODAR Celia</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>36936</t>
         </is>
@@ -4515,7 +4545,7 @@
           <t>CASSINI Maria Luz</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>41627</t>
         </is>
@@ -4573,7 +4603,7 @@
           <t>CONLAN Aisling</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>35814</t>
         </is>
@@ -4631,7 +4661,7 @@
           <t>IFARRAGUERRI Anna Maria</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>39209</t>
         </is>
@@ -4689,7 +4719,7 @@
           <t>FEREKIDOU Maria</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>35434</t>
         </is>
@@ -4747,7 +4777,7 @@
           <t>ITO Yoshika</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>36647</t>
         </is>
@@ -4805,7 +4835,7 @@
           <t>DENHOLLANDER Jazmyne</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>37165</t>
         </is>
@@ -4863,7 +4893,7 @@
           <t>CRAIG Hannah</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>35815</t>
         </is>
@@ -4921,7 +4951,7 @@
           <t>FROEHLICH Thea</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr">
+      <c r="X74" t="inlineStr">
         <is>
           <t>35533</t>
         </is>
@@ -4979,7 +5009,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr">
+      <c r="X75" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -5090,7 +5120,7 @@
           <t>ISMAILOVA Sevinch</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr">
+      <c r="X77" t="inlineStr">
         <is>
           <t>35269</t>
         </is>
@@ -5148,7 +5178,7 @@
           <t>NICHOLAS Ella</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr">
+      <c r="X78" t="inlineStr">
         <is>
           <t>36591</t>
         </is>
@@ -5259,7 +5289,7 @@
           <t>GROENEVELD Jessica</t>
         </is>
       </c>
-      <c r="U80" t="inlineStr">
+      <c r="X80" t="inlineStr">
         <is>
           <t>35542</t>
         </is>
@@ -5317,7 +5347,7 @@
           <t>NEE Ashley</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr">
+      <c r="X81" t="inlineStr">
         <is>
           <t>36363</t>
         </is>
@@ -5375,7 +5405,7 @@
           <t>LEENDERS Claudia</t>
         </is>
       </c>
-      <c r="U82" t="inlineStr">
+      <c r="X82" t="inlineStr">
         <is>
           <t>35331</t>
         </is>
@@ -5433,7 +5463,7 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U83" t="inlineStr">
+      <c r="X83" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -5491,7 +5521,7 @@
           <t>YAZAWA Aki</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr">
+      <c r="X84" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
@@ -5549,7 +5579,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr">
+      <c r="X85" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -5607,7 +5637,7 @@
           <t>LI Tong</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr">
+      <c r="X86" t="inlineStr">
         <is>
           <t>52023</t>
         </is>
@@ -5665,7 +5695,7 @@
           <t>TAKESHITA Yuriko</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr">
+      <c r="X87" t="inlineStr">
         <is>
           <t>36487</t>
         </is>
@@ -5776,7 +5806,7 @@
           <t>GIAI PRON Maria Clara</t>
         </is>
       </c>
-      <c r="U89" t="inlineStr">
+      <c r="X89" t="inlineStr">
         <is>
           <t>35218</t>
         </is>
@@ -5834,7 +5864,7 @@
           <t>NEVARILOVA Kristina</t>
         </is>
       </c>
-      <c r="U90" t="inlineStr">
+      <c r="X90" t="inlineStr">
         <is>
           <t>35467</t>
         </is>
@@ -5892,7 +5922,7 @@
           <t>BORROWS Alison</t>
         </is>
       </c>
-      <c r="U91" t="inlineStr">
+      <c r="X91" t="inlineStr">
         <is>
           <t>38440</t>
         </is>
@@ -5950,7 +5980,7 @@
           <t>MANN Dana</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr">
+      <c r="X92" t="inlineStr">
         <is>
           <t>35369</t>
         </is>
@@ -6008,7 +6038,7 @@
           <t>OBLINGER-PETERS Violetta</t>
         </is>
       </c>
-      <c r="U93" t="inlineStr">
+      <c r="X93" t="inlineStr">
         <is>
           <t>35289</t>
         </is>
@@ -6066,7 +6096,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U94" t="inlineStr">
+      <c r="X94" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -6124,7 +6154,7 @@
           <t>PEROVA Ekaterina</t>
         </is>
       </c>
-      <c r="U95" t="inlineStr">
+      <c r="X95" t="inlineStr">
         <is>
           <t>35131</t>
         </is>
@@ -6182,7 +6212,7 @@
           <t>PEROVA Aleksandra</t>
         </is>
       </c>
-      <c r="U96" t="inlineStr">
+      <c r="X96" t="inlineStr">
         <is>
           <t>35256</t>
         </is>
@@ -6240,7 +6270,7 @@
           <t>GOIKOETXEA Irati</t>
         </is>
       </c>
-      <c r="U97" t="inlineStr">
+      <c r="X97" t="inlineStr">
         <is>
           <t>35761</t>
         </is>
@@ -6298,7 +6328,7 @@
           <t>FRITSCHE Lisa</t>
         </is>
       </c>
-      <c r="U98" t="inlineStr">
+      <c r="X98" t="inlineStr">
         <is>
           <t>39883</t>
         </is>
@@ -6356,7 +6386,7 @@
           <t>BOUZIDI Carole</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr">
+      <c r="X99" t="inlineStr">
         <is>
           <t>35231</t>
         </is>
@@ -6414,7 +6444,7 @@
           <t>VOJTOVA Veronika</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr">
+      <c r="X100" t="inlineStr">
         <is>
           <t>35945</t>
         </is>
@@ -6472,7 +6502,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U101" t="inlineStr">
+      <c r="X101" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -6583,7 +6613,7 @@
           <t>KALISKA Elena</t>
         </is>
       </c>
-      <c r="U103" t="inlineStr">
+      <c r="X103" t="inlineStr">
         <is>
           <t>35366</t>
         </is>
@@ -6641,7 +6671,7 @@
           <t>LEITNER Lisa</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr">
+      <c r="X104" t="inlineStr">
         <is>
           <t>35305</t>
         </is>
@@ -6699,7 +6729,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U105" t="inlineStr">
+      <c r="X105" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -6757,7 +6787,7 @@
           <t>PENNIE Fiona</t>
         </is>
       </c>
-      <c r="U106" t="inlineStr">
+      <c r="X106" t="inlineStr">
         <is>
           <t>35638</t>
         </is>
@@ -6815,7 +6845,7 @@
           <t>KHARITONOVA Marta</t>
         </is>
       </c>
-      <c r="U107" t="inlineStr">
+      <c r="X107" t="inlineStr">
         <is>
           <t>35257</t>
         </is>
@@ -6873,7 +6903,7 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U108" t="inlineStr">
+      <c r="X108" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -6931,7 +6961,7 @@
           <t>LAFONT Marie-Zelia</t>
         </is>
       </c>
-      <c r="U109" t="inlineStr">
+      <c r="X109" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
@@ -6989,7 +7019,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U110" t="inlineStr">
+      <c r="X110" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -7100,7 +7130,7 @@
           <t>MARTINEZ Marta</t>
         </is>
       </c>
-      <c r="U112" t="inlineStr">
+      <c r="X112" t="inlineStr">
         <is>
           <t>35760</t>
         </is>
@@ -7158,7 +7188,7 @@
           <t>HILGERTOVA Stepanka</t>
         </is>
       </c>
-      <c r="U113" t="inlineStr">
+      <c r="X113" t="inlineStr">
         <is>
           <t>35035</t>
         </is>
@@ -7216,7 +7246,7 @@
           <t>KUDEJOVA Katerina</t>
         </is>
       </c>
-      <c r="U114" t="inlineStr">
+      <c r="X114" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
@@ -7274,7 +7304,7 @@
           <t>KRAGELJ Ursa</t>
         </is>
       </c>
-      <c r="U115" t="inlineStr">
+      <c r="X115" t="inlineStr">
         <is>
           <t>36264</t>
         </is>
@@ -7332,7 +7362,7 @@
           <t>FER Emilie</t>
         </is>
       </c>
-      <c r="U116" t="inlineStr">
+      <c r="X116" t="inlineStr">
         <is>
           <t>35314</t>
         </is>
@@ -7390,7 +7420,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U117" t="inlineStr">
+      <c r="X117" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -7448,7 +7478,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U118" t="inlineStr">
+      <c r="X118" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -7506,7 +7536,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U119" t="inlineStr">
+      <c r="X119" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -7564,7 +7594,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U120" t="inlineStr">
+      <c r="X120" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -7872,12 +7902,12 @@
           <t>SHAMSIBOEV Shoxruxmirzo</t>
         </is>
       </c>
-      <c r="U126" t="inlineStr">
+      <c r="X126" t="inlineStr">
         <is>
           <t>67344</t>
         </is>
       </c>
-      <c r="V126" t="inlineStr">
+      <c r="Y126" t="inlineStr">
         <is>
           <t>67346</t>
         </is>
@@ -7940,7 +7970,7 @@
           <t>ZINOVYEV Pavel</t>
         </is>
       </c>
-      <c r="V127" t="inlineStr">
+      <c r="Y127" t="inlineStr">
         <is>
           <t>39682</t>
         </is>
@@ -8003,12 +8033,12 @@
           <t>ERGASHEV Muhibillo</t>
         </is>
       </c>
-      <c r="U128" t="inlineStr">
+      <c r="X128" t="inlineStr">
         <is>
           <t>61155</t>
         </is>
       </c>
-      <c r="V128" t="inlineStr">
+      <c r="Y128" t="inlineStr">
         <is>
           <t>61161</t>
         </is>
@@ -8129,12 +8159,12 @@
           <t>DENNIS Tad</t>
         </is>
       </c>
-      <c r="U130" t="inlineStr">
+      <c r="X130" t="inlineStr">
         <is>
           <t>51904</t>
         </is>
       </c>
-      <c r="V130" t="inlineStr">
+      <c r="Y130" t="inlineStr">
         <is>
           <t>42253</t>
         </is>
@@ -8197,12 +8227,12 @@
           <t>ROSSI Sebastian</t>
         </is>
       </c>
-      <c r="U131" t="inlineStr">
+      <c r="X131" t="inlineStr">
         <is>
           <t>36925</t>
         </is>
       </c>
-      <c r="V131" t="inlineStr">
+      <c r="Y131" t="inlineStr">
         <is>
           <t>36915</t>
         </is>
@@ -8265,12 +8295,12 @@
           <t>SMEDLEY Cameron</t>
         </is>
       </c>
-      <c r="U132" t="inlineStr">
+      <c r="X132" t="inlineStr">
         <is>
           <t>35539</t>
         </is>
       </c>
-      <c r="V132" t="inlineStr">
+      <c r="Y132" t="inlineStr">
         <is>
           <t>35543</t>
         </is>
@@ -8333,12 +8363,12 @@
           <t>CHEN Jin</t>
         </is>
       </c>
-      <c r="U133" t="inlineStr">
+      <c r="X133" t="inlineStr">
         <is>
           <t>42237</t>
         </is>
       </c>
-      <c r="V133" t="inlineStr">
+      <c r="Y133" t="inlineStr">
         <is>
           <t>42238</t>
         </is>
@@ -8401,12 +8431,12 @@
           <t>SILVA Jose</t>
         </is>
       </c>
-      <c r="U134" t="inlineStr">
+      <c r="X134" t="inlineStr">
         <is>
           <t>41649</t>
         </is>
       </c>
-      <c r="V134" t="inlineStr">
+      <c r="Y134" t="inlineStr">
         <is>
           <t>36494</t>
         </is>
@@ -8469,12 +8499,12 @@
           <t>DE SOUZA Rafael</t>
         </is>
       </c>
-      <c r="U135" t="inlineStr">
+      <c r="X135" t="inlineStr">
         <is>
           <t>60498</t>
         </is>
       </c>
-      <c r="V135" t="inlineStr">
+      <c r="Y135" t="inlineStr">
         <is>
           <t>38021</t>
         </is>
@@ -8537,12 +8567,12 @@
           <t>DENG Xiao</t>
         </is>
       </c>
-      <c r="U136" t="inlineStr">
+      <c r="X136" t="inlineStr">
         <is>
           <t>42239</t>
         </is>
       </c>
-      <c r="V136" t="inlineStr">
+      <c r="Y136" t="inlineStr">
         <is>
           <t>42240</t>
         </is>
@@ -8605,7 +8635,7 @@
           <t>SASAKI Tsubasa</t>
         </is>
       </c>
-      <c r="U137" t="inlineStr">
+      <c r="X137" t="inlineStr">
         <is>
           <t>41610</t>
         </is>
@@ -8668,12 +8698,12 @@
           <t>OLIVEIRA Anderson</t>
         </is>
       </c>
-      <c r="U138" t="inlineStr">
+      <c r="X138" t="inlineStr">
         <is>
           <t>38018</t>
         </is>
       </c>
-      <c r="V138" t="inlineStr">
+      <c r="Y138" t="inlineStr">
         <is>
           <t>38020</t>
         </is>
@@ -8736,12 +8766,12 @@
           <t>OBRAZTSOV Maxim</t>
         </is>
       </c>
-      <c r="U139" t="inlineStr">
+      <c r="X139" t="inlineStr">
         <is>
           <t>35770</t>
         </is>
       </c>
-      <c r="V139" t="inlineStr">
+      <c r="Y139" t="inlineStr">
         <is>
           <t>35767</t>
         </is>
@@ -8804,12 +8834,12 @@
           <t>HUANG Yongze</t>
         </is>
       </c>
-      <c r="U140" t="inlineStr">
+      <c r="X140" t="inlineStr">
         <is>
           <t>52028</t>
         </is>
       </c>
-      <c r="V140" t="inlineStr">
+      <c r="Y140" t="inlineStr">
         <is>
           <t>52029</t>
         </is>
@@ -8872,12 +8902,12 @@
           <t>WERRO Simon</t>
         </is>
       </c>
-      <c r="U141" t="inlineStr">
+      <c r="X141" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
       </c>
-      <c r="V141" t="inlineStr">
+      <c r="Y141" t="inlineStr">
         <is>
           <t>35424</t>
         </is>
@@ -8940,12 +8970,12 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U142" t="inlineStr">
+      <c r="X142" t="inlineStr">
         <is>
           <t>35068</t>
         </is>
       </c>
-      <c r="V142" t="inlineStr">
+      <c r="Y142" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -9008,7 +9038,7 @@
           <t>PITT Greg</t>
         </is>
       </c>
-      <c r="U143" t="inlineStr">
+      <c r="X143" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -9071,12 +9101,12 @@
           <t>USHAKOV Artem</t>
         </is>
       </c>
-      <c r="U144" t="inlineStr">
+      <c r="X144" t="inlineStr">
         <is>
           <t>35454</t>
         </is>
       </c>
-      <c r="V144" t="inlineStr">
+      <c r="Y144" t="inlineStr">
         <is>
           <t>35455</t>
         </is>
@@ -9139,12 +9169,12 @@
           <t>KERVELLA Loic</t>
         </is>
       </c>
-      <c r="U145" t="inlineStr">
+      <c r="X145" t="inlineStr">
         <is>
           <t>35671</t>
         </is>
       </c>
-      <c r="V145" t="inlineStr">
+      <c r="Y145" t="inlineStr">
         <is>
           <t>35672</t>
         </is>
@@ -9207,12 +9237,12 @@
           <t>VRZAN Jakub</t>
         </is>
       </c>
-      <c r="U146" t="inlineStr">
+      <c r="X146" t="inlineStr">
         <is>
           <t>35042</t>
         </is>
       </c>
-      <c r="V146" t="inlineStr">
+      <c r="Y146" t="inlineStr">
         <is>
           <t>35043</t>
         </is>
@@ -9275,12 +9305,12 @@
           <t>PEREZ Jesus</t>
         </is>
       </c>
-      <c r="U147" t="inlineStr">
+      <c r="X147" t="inlineStr">
         <is>
           <t>35757</t>
         </is>
       </c>
-      <c r="V147" t="inlineStr">
+      <c r="Y147" t="inlineStr">
         <is>
           <t>36091</t>
         </is>
@@ -9343,12 +9373,12 @@
           <t>MAJERCZAK Grzegorz</t>
         </is>
       </c>
-      <c r="U148" t="inlineStr">
+      <c r="X148" t="inlineStr">
         <is>
           <t>35085</t>
         </is>
       </c>
-      <c r="V148" t="inlineStr">
+      <c r="Y148" t="inlineStr">
         <is>
           <t>35086</t>
         </is>
@@ -9411,12 +9441,12 @@
           <t>MUELLER Kevin</t>
         </is>
       </c>
-      <c r="U149" t="inlineStr">
+      <c r="X149" t="inlineStr">
         <is>
           <t>35148</t>
         </is>
       </c>
-      <c r="V149" t="inlineStr">
+      <c r="Y149" t="inlineStr">
         <is>
           <t>35149</t>
         </is>
@@ -9479,12 +9509,12 @@
           <t>BATIK Jan</t>
         </is>
       </c>
-      <c r="U150" t="inlineStr">
+      <c r="X150" t="inlineStr">
         <is>
           <t>35368</t>
         </is>
       </c>
-      <c r="V150" t="inlineStr">
+      <c r="Y150" t="inlineStr">
         <is>
           <t>35367</t>
         </is>
@@ -9542,7 +9572,7 @@
           <t>BEYAZOGLU Buse</t>
         </is>
       </c>
-      <c r="U151" t="inlineStr">
+      <c r="X151" t="inlineStr">
         <is>
           <t>61581</t>
         </is>
@@ -9653,7 +9683,7 @@
           <t>SAMLAL Jihane</t>
         </is>
       </c>
-      <c r="U153" t="inlineStr">
+      <c r="X153" t="inlineStr">
         <is>
           <t>38424</t>
         </is>
@@ -9711,7 +9741,7 @@
           <t>XU Yanru</t>
         </is>
       </c>
-      <c r="U154" t="inlineStr">
+      <c r="X154" t="inlineStr">
         <is>
           <t>63801</t>
         </is>
@@ -9769,7 +9799,7 @@
           <t>SMIRNOVA Yekaterina</t>
         </is>
       </c>
-      <c r="U155" t="inlineStr">
+      <c r="X155" t="inlineStr">
         <is>
           <t>38002</t>
         </is>
@@ -9827,7 +9857,7 @@
           <t>SAETHER Mariann</t>
         </is>
       </c>
-      <c r="U156" t="inlineStr">
+      <c r="X156" t="inlineStr">
         <is>
           <t>53420</t>
         </is>
@@ -9885,7 +9915,7 @@
           <t>BARANAUSKAITE Erika</t>
         </is>
       </c>
-      <c r="U157" t="inlineStr">
+      <c r="X157" t="inlineStr">
         <is>
           <t>35622</t>
         </is>
@@ -9943,7 +9973,7 @@
           <t>JAMILI Hind</t>
         </is>
       </c>
-      <c r="U158" t="inlineStr">
+      <c r="X158" t="inlineStr">
         <is>
           <t>43390</t>
         </is>
@@ -10001,7 +10031,7 @@
           <t>REINOSO Sofia</t>
         </is>
       </c>
-      <c r="U159" t="inlineStr">
+      <c r="X159" t="inlineStr">
         <is>
           <t>45745</t>
         </is>
@@ -10059,7 +10089,7 @@
           <t>JODAR Celia</t>
         </is>
       </c>
-      <c r="U160" t="inlineStr">
+      <c r="X160" t="inlineStr">
         <is>
           <t>36936</t>
         </is>
@@ -10117,7 +10147,7 @@
           <t>CASSINI Maria Luz</t>
         </is>
       </c>
-      <c r="U161" t="inlineStr">
+      <c r="X161" t="inlineStr">
         <is>
           <t>41627</t>
         </is>
@@ -10175,7 +10205,7 @@
           <t>CONLAN Aisling</t>
         </is>
       </c>
-      <c r="U162" t="inlineStr">
+      <c r="X162" t="inlineStr">
         <is>
           <t>35814</t>
         </is>
@@ -10233,7 +10263,7 @@
           <t>IFARRAGUERRI Anna Maria</t>
         </is>
       </c>
-      <c r="U163" t="inlineStr">
+      <c r="X163" t="inlineStr">
         <is>
           <t>39209</t>
         </is>
@@ -10291,7 +10321,7 @@
           <t>FEREKIDOU Maria</t>
         </is>
       </c>
-      <c r="U164" t="inlineStr">
+      <c r="X164" t="inlineStr">
         <is>
           <t>35434</t>
         </is>
@@ -10349,7 +10379,7 @@
           <t>ITO Yoshika</t>
         </is>
       </c>
-      <c r="U165" t="inlineStr">
+      <c r="X165" t="inlineStr">
         <is>
           <t>36647</t>
         </is>
@@ -10407,7 +10437,7 @@
           <t>DENHOLLANDER Jazmyne</t>
         </is>
       </c>
-      <c r="U166" t="inlineStr">
+      <c r="X166" t="inlineStr">
         <is>
           <t>37165</t>
         </is>
@@ -10465,7 +10495,7 @@
           <t>CRAIG Hannah</t>
         </is>
       </c>
-      <c r="U167" t="inlineStr">
+      <c r="X167" t="inlineStr">
         <is>
           <t>35815</t>
         </is>
@@ -10523,7 +10553,7 @@
           <t>FROEHLICH Thea</t>
         </is>
       </c>
-      <c r="U168" t="inlineStr">
+      <c r="X168" t="inlineStr">
         <is>
           <t>35533</t>
         </is>
@@ -10581,7 +10611,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U169" t="inlineStr">
+      <c r="X169" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -10692,7 +10722,7 @@
           <t>ISMAILOVA Sevinch</t>
         </is>
       </c>
-      <c r="U171" t="inlineStr">
+      <c r="X171" t="inlineStr">
         <is>
           <t>35269</t>
         </is>
@@ -10750,7 +10780,7 @@
           <t>NICHOLAS Ella</t>
         </is>
       </c>
-      <c r="U172" t="inlineStr">
+      <c r="X172" t="inlineStr">
         <is>
           <t>36591</t>
         </is>
@@ -10861,7 +10891,7 @@
           <t>GROENEVELD Jessica</t>
         </is>
       </c>
-      <c r="U174" t="inlineStr">
+      <c r="X174" t="inlineStr">
         <is>
           <t>35542</t>
         </is>
@@ -10919,7 +10949,7 @@
           <t>NEE Ashley</t>
         </is>
       </c>
-      <c r="U175" t="inlineStr">
+      <c r="X175" t="inlineStr">
         <is>
           <t>36363</t>
         </is>
@@ -10977,7 +11007,7 @@
           <t>LEENDERS Claudia</t>
         </is>
       </c>
-      <c r="U176" t="inlineStr">
+      <c r="X176" t="inlineStr">
         <is>
           <t>35331</t>
         </is>
@@ -11035,7 +11065,7 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U177" t="inlineStr">
+      <c r="X177" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -11093,7 +11123,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U178" t="inlineStr">
+      <c r="X178" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -11151,7 +11181,7 @@
           <t>LI Tong</t>
         </is>
       </c>
-      <c r="U179" t="inlineStr">
+      <c r="X179" t="inlineStr">
         <is>
           <t>52023</t>
         </is>
@@ -11209,7 +11239,7 @@
           <t>TAKESHITA Yuriko</t>
         </is>
       </c>
-      <c r="U180" t="inlineStr">
+      <c r="X180" t="inlineStr">
         <is>
           <t>36487</t>
         </is>
@@ -11320,7 +11350,7 @@
           <t>GIAI PRON Maria Clara</t>
         </is>
       </c>
-      <c r="U182" t="inlineStr">
+      <c r="X182" t="inlineStr">
         <is>
           <t>35218</t>
         </is>
@@ -11378,7 +11408,7 @@
           <t>NEVARILOVA Kristina</t>
         </is>
       </c>
-      <c r="U183" t="inlineStr">
+      <c r="X183" t="inlineStr">
         <is>
           <t>35467</t>
         </is>
@@ -11436,7 +11466,7 @@
           <t>BORROWS Alison</t>
         </is>
       </c>
-      <c r="U184" t="inlineStr">
+      <c r="X184" t="inlineStr">
         <is>
           <t>38440</t>
         </is>
@@ -11494,7 +11524,7 @@
           <t>MANN Dana</t>
         </is>
       </c>
-      <c r="U185" t="inlineStr">
+      <c r="X185" t="inlineStr">
         <is>
           <t>35369</t>
         </is>
@@ -11552,7 +11582,7 @@
           <t>OBLINGER-PETERS Violetta</t>
         </is>
       </c>
-      <c r="U186" t="inlineStr">
+      <c r="X186" t="inlineStr">
         <is>
           <t>35289</t>
         </is>
@@ -11610,7 +11640,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U187" t="inlineStr">
+      <c r="X187" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -11668,7 +11698,7 @@
           <t>PEROVA Ekaterina</t>
         </is>
       </c>
-      <c r="U188" t="inlineStr">
+      <c r="X188" t="inlineStr">
         <is>
           <t>35131</t>
         </is>
@@ -11726,7 +11756,7 @@
           <t>GOIKOETXEA Irati</t>
         </is>
       </c>
-      <c r="U189" t="inlineStr">
+      <c r="X189" t="inlineStr">
         <is>
           <t>35761</t>
         </is>
@@ -11784,7 +11814,7 @@
           <t>FRITSCHE Lisa</t>
         </is>
       </c>
-      <c r="U190" t="inlineStr">
+      <c r="X190" t="inlineStr">
         <is>
           <t>39883</t>
         </is>
@@ -11842,7 +11872,7 @@
           <t>BOUZIDI Carole</t>
         </is>
       </c>
-      <c r="U191" t="inlineStr">
+      <c r="X191" t="inlineStr">
         <is>
           <t>35231</t>
         </is>
@@ -11900,7 +11930,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U192" t="inlineStr">
+      <c r="X192" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -11958,7 +11988,7 @@
           <t>KALISKA Elena</t>
         </is>
       </c>
-      <c r="U193" t="inlineStr">
+      <c r="X193" t="inlineStr">
         <is>
           <t>35366</t>
         </is>
@@ -12016,7 +12046,7 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U194" t="inlineStr">
+      <c r="X194" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -12074,7 +12104,7 @@
           <t>MARTINEZ Marta</t>
         </is>
       </c>
-      <c r="U195" t="inlineStr">
+      <c r="X195" t="inlineStr">
         <is>
           <t>35760</t>
         </is>
@@ -12132,7 +12162,7 @@
           <t>HILGERTOVA Stepanka</t>
         </is>
       </c>
-      <c r="U196" t="inlineStr">
+      <c r="X196" t="inlineStr">
         <is>
           <t>35035</t>
         </is>
@@ -12435,7 +12465,7 @@
           <t>KARIMIMANJILI Mahdi</t>
         </is>
       </c>
-      <c r="U202" t="inlineStr">
+      <c r="X202" t="inlineStr">
         <is>
           <t>64730</t>
         </is>
@@ -12493,7 +12523,7 @@
           <t>DOBY Mathieu</t>
         </is>
       </c>
-      <c r="U203" t="inlineStr">
+      <c r="X203" t="inlineStr">
         <is>
           <t>35292</t>
         </is>
@@ -12551,7 +12581,7 @@
           <t>CHEN Bo-Wun</t>
         </is>
       </c>
-      <c r="U204" t="inlineStr">
+      <c r="X204" t="inlineStr">
         <is>
           <t>36365</t>
         </is>
@@ -12609,7 +12639,7 @@
           <t>LI Gongte</t>
         </is>
       </c>
-      <c r="U205" t="inlineStr">
+      <c r="X205" t="inlineStr">
         <is>
           <t>51820</t>
         </is>
@@ -12667,7 +12697,7 @@
           <t>KIM Beomsoo</t>
         </is>
       </c>
-      <c r="U206" t="inlineStr">
+      <c r="X206" t="inlineStr">
         <is>
           <t>64845</t>
         </is>
@@ -12725,7 +12755,7 @@
           <t>LAVIOLETTE Yannick</t>
         </is>
       </c>
-      <c r="U207" t="inlineStr">
+      <c r="X207" t="inlineStr">
         <is>
           <t>43343</t>
         </is>
@@ -12836,7 +12866,7 @@
           <t>BOURHIS Yves</t>
         </is>
       </c>
-      <c r="U209" t="inlineStr">
+      <c r="X209" t="inlineStr">
         <is>
           <t>63237</t>
         </is>
@@ -12894,7 +12924,7 @@
           <t>MALEY Kynan</t>
         </is>
       </c>
-      <c r="U210" t="inlineStr">
+      <c r="X210" t="inlineStr">
         <is>
           <t>36524</t>
         </is>
@@ -12952,7 +12982,7 @@
           <t>CESPEDES PEREZ Arnaldo</t>
         </is>
       </c>
-      <c r="U211" t="inlineStr">
+      <c r="X211" t="inlineStr">
         <is>
           <t>41634</t>
         </is>
@@ -13010,7 +13040,7 @@
           <t>COCHRANE Jake</t>
         </is>
       </c>
-      <c r="U212" t="inlineStr">
+      <c r="X212" t="inlineStr">
         <is>
           <t>60124</t>
         </is>
@@ -13068,7 +13098,7 @@
           <t>OVCHINNIKOV Aleksandr</t>
         </is>
       </c>
-      <c r="U213" t="inlineStr">
+      <c r="X213" t="inlineStr">
         <is>
           <t>39134</t>
         </is>
@@ -13126,7 +13156,7 @@
           <t>WANG Sheng</t>
         </is>
       </c>
-      <c r="U214" t="inlineStr">
+      <c r="X214" t="inlineStr">
         <is>
           <t>60989</t>
         </is>
@@ -13184,7 +13214,7 @@
           <t>OH Yeachan</t>
         </is>
       </c>
-      <c r="U215" t="inlineStr">
+      <c r="X215" t="inlineStr">
         <is>
           <t>42399</t>
         </is>
@@ -13242,7 +13272,7 @@
           <t>CHEN Fangjia</t>
         </is>
       </c>
-      <c r="U216" t="inlineStr">
+      <c r="X216" t="inlineStr">
         <is>
           <t>42638</t>
         </is>
@@ -13300,7 +13330,7 @@
           <t>WEWEGE Donovan</t>
         </is>
       </c>
-      <c r="U217" t="inlineStr">
+      <c r="X217" t="inlineStr">
         <is>
           <t>39241</t>
         </is>
@@ -13411,7 +13441,7 @@
           <t>DOMENJO Jordi</t>
         </is>
       </c>
-      <c r="U219" t="inlineStr">
+      <c r="X219" t="inlineStr">
         <is>
           <t>35739</t>
         </is>
@@ -13469,7 +13499,7 @@
           <t>THWAITE James</t>
         </is>
       </c>
-      <c r="U220" t="inlineStr">
+      <c r="X220" t="inlineStr">
         <is>
           <t>51862</t>
         </is>
@@ -13527,7 +13557,7 @@
           <t>LIU Chin-Han</t>
         </is>
       </c>
-      <c r="U221" t="inlineStr">
+      <c r="X221" t="inlineStr">
         <is>
           <t>51894</t>
         </is>
@@ -13585,7 +13615,7 @@
           <t>DEMIRCI Ismail</t>
         </is>
       </c>
-      <c r="U222" t="inlineStr">
+      <c r="X222" t="inlineStr">
         <is>
           <t>39914</t>
         </is>
@@ -13643,7 +13673,7 @@
           <t>CHAIDET Yutthakan</t>
         </is>
       </c>
-      <c r="U223" t="inlineStr">
+      <c r="X223" t="inlineStr">
         <is>
           <t>51798</t>
         </is>
@@ -13754,7 +13784,7 @@
           <t>SASAKI Shota</t>
         </is>
       </c>
-      <c r="U225" t="inlineStr">
+      <c r="X225" t="inlineStr">
         <is>
           <t>41610</t>
         </is>
@@ -13812,7 +13842,7 @@
           <t>HIGGINS Shaun</t>
         </is>
       </c>
-      <c r="U226" t="inlineStr">
+      <c r="X226" t="inlineStr">
         <is>
           <t>36655</t>
         </is>
@@ -13870,7 +13900,7 @@
           <t>SILVA Jose</t>
         </is>
       </c>
-      <c r="U227" t="inlineStr">
+      <c r="X227" t="inlineStr">
         <is>
           <t>36494</t>
         </is>
@@ -13981,7 +14011,7 @@
           <t>SERRA Thiago</t>
         </is>
       </c>
-      <c r="U229" t="inlineStr">
+      <c r="X229" t="inlineStr">
         <is>
           <t>41647</t>
         </is>
@@ -14039,7 +14069,7 @@
           <t>BOURHIS Jean Pierre</t>
         </is>
       </c>
-      <c r="U230" t="inlineStr">
+      <c r="X230" t="inlineStr">
         <is>
           <t>36968</t>
         </is>
@@ -14097,7 +14127,7 @@
           <t>THOMAS Martin</t>
         </is>
       </c>
-      <c r="U231" t="inlineStr">
+      <c r="X231" t="inlineStr">
         <is>
           <t>35412</t>
         </is>
@@ -14208,7 +14238,7 @@
           <t>GIBB Benjamin</t>
         </is>
       </c>
-      <c r="U233" t="inlineStr">
+      <c r="X233" t="inlineStr">
         <is>
           <t>36711</t>
         </is>
@@ -14266,7 +14296,7 @@
           <t>CURCEL Leonardo</t>
         </is>
       </c>
-      <c r="U234" t="inlineStr">
+      <c r="X234" t="inlineStr">
         <is>
           <t>38014</t>
         </is>
@@ -14324,7 +14354,7 @@
           <t>SZTUBA Igor</t>
         </is>
       </c>
-      <c r="U235" t="inlineStr">
+      <c r="X235" t="inlineStr">
         <is>
           <t>35087</t>
         </is>
@@ -14435,7 +14465,7 @@
           <t>SETKIN Kirill</t>
         </is>
       </c>
-      <c r="U237" t="inlineStr">
+      <c r="X237" t="inlineStr">
         <is>
           <t>35457</t>
         </is>
@@ -14493,7 +14523,7 @@
           <t>HODSON Ethan</t>
         </is>
       </c>
-      <c r="U238" t="inlineStr">
+      <c r="X238" t="inlineStr">
         <is>
           <t>38437</t>
         </is>
@@ -14551,7 +14581,7 @@
           <t>JEGOU Liam</t>
         </is>
       </c>
-      <c r="U239" t="inlineStr">
+      <c r="X239" t="inlineStr">
         <is>
           <t>35820</t>
         </is>
@@ -14609,7 +14639,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U240" t="inlineStr">
+      <c r="X240" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -14667,7 +14697,7 @@
           <t>CECCON Paolo</t>
         </is>
       </c>
-      <c r="U241" t="inlineStr">
+      <c r="X241" t="inlineStr">
         <is>
           <t>39903</t>
         </is>
@@ -14725,7 +14755,7 @@
           <t>TRATSIAK Viktar</t>
         </is>
       </c>
-      <c r="U242" t="inlineStr">
+      <c r="X242" t="inlineStr">
         <is>
           <t>35270</t>
         </is>
@@ -14836,7 +14866,7 @@
           <t>ROSSI Sebastian</t>
         </is>
       </c>
-      <c r="U244" t="inlineStr">
+      <c r="X244" t="inlineStr">
         <is>
           <t>36915</t>
         </is>
@@ -14894,7 +14924,7 @@
           <t>SMEDLEY Cameron</t>
         </is>
       </c>
-      <c r="U245" t="inlineStr">
+      <c r="X245" t="inlineStr">
         <is>
           <t>35543</t>
         </is>
@@ -14952,7 +14982,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U246" t="inlineStr">
+      <c r="X246" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -15010,7 +15040,7 @@
           <t>JEFFERY Robin</t>
         </is>
       </c>
-      <c r="U247" t="inlineStr">
+      <c r="X247" t="inlineStr">
         <is>
           <t>36525</t>
         </is>
@@ -15068,7 +15098,7 @@
           <t>GONDEK Kacper</t>
         </is>
       </c>
-      <c r="U248" t="inlineStr">
+      <c r="X248" t="inlineStr">
         <is>
           <t>35472</t>
         </is>
@@ -15126,7 +15156,7 @@
           <t>ERGUIN Jon</t>
         </is>
       </c>
-      <c r="U249" t="inlineStr">
+      <c r="X249" t="inlineStr">
         <is>
           <t>35740</t>
         </is>
@@ -15184,7 +15214,7 @@
           <t>JANE Michal</t>
         </is>
       </c>
-      <c r="U250" t="inlineStr">
+      <c r="X250" t="inlineStr">
         <is>
           <t>35059</t>
         </is>
@@ -15242,7 +15272,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U251" t="inlineStr">
+      <c r="X251" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -15300,7 +15330,7 @@
           <t>LIPATOV Aleksandr</t>
         </is>
       </c>
-      <c r="U252" t="inlineStr">
+      <c r="X252" t="inlineStr">
         <is>
           <t>35451</t>
         </is>
@@ -15358,7 +15388,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U253" t="inlineStr">
+      <c r="X253" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -15416,7 +15446,7 @@
           <t>COLAZINGARI Roberto</t>
         </is>
       </c>
-      <c r="U254" t="inlineStr">
+      <c r="X254" t="inlineStr">
         <is>
           <t>35223</t>
         </is>
@@ -15474,7 +15504,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U255" t="inlineStr">
+      <c r="X255" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -15532,7 +15562,7 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U256" t="inlineStr">
+      <c r="X256" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -15590,7 +15620,7 @@
           <t>PESCHIER Nicolas</t>
         </is>
       </c>
-      <c r="U257" t="inlineStr">
+      <c r="X257" t="inlineStr">
         <is>
           <t>35401</t>
         </is>
@@ -15648,7 +15678,7 @@
           <t>KOECHLIN Thomas</t>
         </is>
       </c>
-      <c r="U258" t="inlineStr">
+      <c r="X258" t="inlineStr">
         <is>
           <t>35419</t>
         </is>
@@ -15706,7 +15736,7 @@
           <t>TILLARD Pierre-Antoine</t>
         </is>
       </c>
-      <c r="U259" t="inlineStr">
+      <c r="X259" t="inlineStr">
         <is>
           <t>35413</t>
         </is>
@@ -15764,7 +15794,7 @@
           <t>MARINIC Matija</t>
         </is>
       </c>
-      <c r="U260" t="inlineStr">
+      <c r="X260" t="inlineStr">
         <is>
           <t>35595</t>
         </is>
@@ -15822,7 +15852,7 @@
           <t>CIPRESSI Stefano</t>
         </is>
       </c>
-      <c r="U261" t="inlineStr">
+      <c r="X261" t="inlineStr">
         <is>
           <t>35495</t>
         </is>
@@ -15880,7 +15910,7 @@
           <t>RAK Tomas</t>
         </is>
       </c>
-      <c r="U262" t="inlineStr">
+      <c r="X262" t="inlineStr">
         <is>
           <t>35056</t>
         </is>
@@ -15938,7 +15968,7 @@
           <t>HANEDA Takuya</t>
         </is>
       </c>
-      <c r="U263" t="inlineStr">
+      <c r="X263" t="inlineStr">
         <is>
           <t>36481</t>
         </is>
@@ -15996,7 +16026,7 @@
           <t>ELOSEGI Ander</t>
         </is>
       </c>
-      <c r="U264" t="inlineStr">
+      <c r="X264" t="inlineStr">
         <is>
           <t>35785</t>
         </is>
@@ -16054,7 +16084,7 @@
           <t>LENARCIC Jure</t>
         </is>
       </c>
-      <c r="U265" t="inlineStr">
+      <c r="X265" t="inlineStr">
         <is>
           <t>36259</t>
         </is>
@@ -16112,7 +16142,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U266" t="inlineStr">
+      <c r="X266" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -16170,7 +16200,7 @@
           <t>JEZEK Stanislav</t>
         </is>
       </c>
-      <c r="U267" t="inlineStr">
+      <c r="X267" t="inlineStr">
         <is>
           <t>35037</t>
         </is>
@@ -16228,7 +16258,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U268" t="inlineStr">
+      <c r="X268" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -16286,7 +16316,7 @@
           <t>TASIADIS Sideris</t>
         </is>
       </c>
-      <c r="U269" t="inlineStr">
+      <c r="X269" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
@@ -16344,7 +16374,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U270" t="inlineStr">
+      <c r="X270" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -16402,7 +16432,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U271" t="inlineStr">
+      <c r="X271" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -16460,7 +16490,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U272" t="inlineStr">
+      <c r="X272" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -16518,7 +16548,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U273" t="inlineStr">
+      <c r="X273" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -16576,7 +16606,7 @@
           <t>FLORENCE David</t>
         </is>
       </c>
-      <c r="U274" t="inlineStr">
+      <c r="X274" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -16634,7 +16664,7 @@
           <t>O'FERRALL Caoimhe</t>
         </is>
       </c>
-      <c r="U275" t="inlineStr">
+      <c r="X275" t="inlineStr">
         <is>
           <t>61007</t>
         </is>
@@ -16745,7 +16775,7 @@
           <t>YAGI Airi</t>
         </is>
       </c>
-      <c r="U277" t="inlineStr">
+      <c r="X277" t="inlineStr">
         <is>
           <t>37756</t>
         </is>
@@ -16803,7 +16833,7 @@
           <t>CHEN Wei-Han</t>
         </is>
       </c>
-      <c r="U278" t="inlineStr">
+      <c r="X278" t="inlineStr">
         <is>
           <t>61630</t>
         </is>
@@ -16861,7 +16891,7 @@
           <t>KUBBE Kira</t>
         </is>
       </c>
-      <c r="U279" t="inlineStr">
+      <c r="X279" t="inlineStr">
         <is>
           <t>43464</t>
         </is>
@@ -16919,7 +16949,7 @@
           <t>SATO Ayano</t>
         </is>
       </c>
-      <c r="U280" t="inlineStr">
+      <c r="X280" t="inlineStr">
         <is>
           <t>60374</t>
         </is>
@@ -16977,7 +17007,7 @@
           <t>MURZINA Juta</t>
         </is>
       </c>
-      <c r="U281" t="inlineStr">
+      <c r="X281" t="inlineStr">
         <is>
           <t>39930</t>
         </is>
@@ -17035,7 +17065,7 @@
           <t>HERZOG Andrea</t>
         </is>
       </c>
-      <c r="U282" t="inlineStr">
+      <c r="X282" t="inlineStr">
         <is>
           <t>55099</t>
         </is>
@@ -17093,7 +17123,7 @@
           <t>MUKHGALEEVA Polina</t>
         </is>
       </c>
-      <c r="U283" t="inlineStr">
+      <c r="X283" t="inlineStr">
         <is>
           <t>35768</t>
         </is>
@@ -17151,7 +17181,7 @@
           <t>DUANGLAHWA Atcharaporn</t>
         </is>
       </c>
-      <c r="U284" t="inlineStr">
+      <c r="X284" t="inlineStr">
         <is>
           <t>61799</t>
         </is>
@@ -17262,7 +17292,7 @@
           <t>BIZJAK Nina</t>
         </is>
       </c>
-      <c r="U286" t="inlineStr">
+      <c r="X286" t="inlineStr">
         <is>
           <t>39984</t>
         </is>
@@ -17320,7 +17350,7 @@
           <t>TRAVERS Kelly</t>
         </is>
       </c>
-      <c r="U287" t="inlineStr">
+      <c r="X287" t="inlineStr">
         <is>
           <t>51643</t>
         </is>
@@ -17378,7 +17408,7 @@
           <t>DANIELS Haley</t>
         </is>
       </c>
-      <c r="U288" t="inlineStr">
+      <c r="X288" t="inlineStr">
         <is>
           <t>36260</t>
         </is>
@@ -17436,7 +17466,7 @@
           <t>JANCZY Justyna</t>
         </is>
       </c>
-      <c r="U289" t="inlineStr">
+      <c r="X289" t="inlineStr">
         <is>
           <t>43975</t>
         </is>
@@ -17547,7 +17577,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U291" t="inlineStr">
+      <c r="X291" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -17605,7 +17635,7 @@
           <t>SABITOVA Zulfia</t>
         </is>
       </c>
-      <c r="U292" t="inlineStr">
+      <c r="X292" t="inlineStr">
         <is>
           <t>40572</t>
         </is>
@@ -17663,7 +17693,7 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U293" t="inlineStr">
+      <c r="X293" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -17721,7 +17751,7 @@
           <t>TIXIER Cecile</t>
         </is>
       </c>
-      <c r="U294" t="inlineStr">
+      <c r="X294" t="inlineStr">
         <is>
           <t>35687</t>
         </is>
@@ -17779,7 +17809,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U295" t="inlineStr">
+      <c r="X295" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -17837,7 +17867,7 @@
           <t>JACQUET Claire</t>
         </is>
       </c>
-      <c r="U296" t="inlineStr">
+      <c r="X296" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
@@ -17895,7 +17925,7 @@
           <t>VAN DER KNIJFF Annebel</t>
         </is>
       </c>
-      <c r="U297" t="inlineStr">
+      <c r="X297" t="inlineStr">
         <is>
           <t>39945</t>
         </is>
@@ -17953,7 +17983,7 @@
           <t>BORROWS Alison</t>
         </is>
       </c>
-      <c r="U298" t="inlineStr">
+      <c r="X298" t="inlineStr">
         <is>
           <t>38440</t>
         </is>
@@ -18011,7 +18041,7 @@
           <t>GIBSON Eilidh</t>
         </is>
       </c>
-      <c r="U299" t="inlineStr">
+      <c r="X299" t="inlineStr">
         <is>
           <t>36708</t>
         </is>
@@ -18069,7 +18099,7 @@
           <t>DOBROTVORSKA Viktoriia</t>
         </is>
       </c>
-      <c r="U300" t="inlineStr">
+      <c r="X300" t="inlineStr">
         <is>
           <t>35526</t>
         </is>
@@ -18127,7 +18157,7 @@
           <t>STOECKLIN Lena</t>
         </is>
       </c>
-      <c r="U301" t="inlineStr">
+      <c r="X301" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
@@ -18185,7 +18215,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U302" t="inlineStr">
+      <c r="X302" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -18243,7 +18273,7 @@
           <t>JANCOVA Monika</t>
         </is>
       </c>
-      <c r="U303" t="inlineStr">
+      <c r="X303" t="inlineStr">
         <is>
           <t>36015</t>
         </is>
@@ -18354,7 +18384,7 @@
           <t>SCHMID Julia</t>
         </is>
       </c>
-      <c r="U305" t="inlineStr">
+      <c r="X305" t="inlineStr">
         <is>
           <t>35309</t>
         </is>
@@ -18465,7 +18495,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U307" t="inlineStr">
+      <c r="X307" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -18523,7 +18553,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U308" t="inlineStr">
+      <c r="X308" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -18581,7 +18611,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U309" t="inlineStr">
+      <c r="X309" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -18692,7 +18722,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U311" t="inlineStr">
+      <c r="X311" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -18995,7 +19025,7 @@
           <t>KARIMIMANJILI Mahdi</t>
         </is>
       </c>
-      <c r="U317" t="inlineStr">
+      <c r="X317" t="inlineStr">
         <is>
           <t>64730</t>
         </is>
@@ -19053,7 +19083,7 @@
           <t>DOBY Mathieu</t>
         </is>
       </c>
-      <c r="U318" t="inlineStr">
+      <c r="X318" t="inlineStr">
         <is>
           <t>35292</t>
         </is>
@@ -19111,7 +19141,7 @@
           <t>CHEN Bo-Wun</t>
         </is>
       </c>
-      <c r="U319" t="inlineStr">
+      <c r="X319" t="inlineStr">
         <is>
           <t>36365</t>
         </is>
@@ -19169,7 +19199,7 @@
           <t>LI Gongte</t>
         </is>
       </c>
-      <c r="U320" t="inlineStr">
+      <c r="X320" t="inlineStr">
         <is>
           <t>51820</t>
         </is>
@@ -19227,7 +19257,7 @@
           <t>KIM Beomsoo</t>
         </is>
       </c>
-      <c r="U321" t="inlineStr">
+      <c r="X321" t="inlineStr">
         <is>
           <t>64845</t>
         </is>
@@ -19285,7 +19315,7 @@
           <t>LAVIOLETTE Yannick</t>
         </is>
       </c>
-      <c r="U322" t="inlineStr">
+      <c r="X322" t="inlineStr">
         <is>
           <t>43343</t>
         </is>
@@ -19396,7 +19426,7 @@
           <t>BOURHIS Yves</t>
         </is>
       </c>
-      <c r="U324" t="inlineStr">
+      <c r="X324" t="inlineStr">
         <is>
           <t>63237</t>
         </is>
@@ -19454,7 +19484,7 @@
           <t>MALEY Kynan</t>
         </is>
       </c>
-      <c r="U325" t="inlineStr">
+      <c r="X325" t="inlineStr">
         <is>
           <t>36524</t>
         </is>
@@ -19512,7 +19542,7 @@
           <t>CESPEDES PEREZ Arnaldo</t>
         </is>
       </c>
-      <c r="U326" t="inlineStr">
+      <c r="X326" t="inlineStr">
         <is>
           <t>41634</t>
         </is>
@@ -19570,7 +19600,7 @@
           <t>COCHRANE Jake</t>
         </is>
       </c>
-      <c r="U327" t="inlineStr">
+      <c r="X327" t="inlineStr">
         <is>
           <t>60124</t>
         </is>
@@ -19628,7 +19658,7 @@
           <t>OVCHINNIKOV Aleksandr</t>
         </is>
       </c>
-      <c r="U328" t="inlineStr">
+      <c r="X328" t="inlineStr">
         <is>
           <t>39134</t>
         </is>
@@ -19686,7 +19716,7 @@
           <t>WANG Sheng</t>
         </is>
       </c>
-      <c r="U329" t="inlineStr">
+      <c r="X329" t="inlineStr">
         <is>
           <t>60989</t>
         </is>
@@ -19744,7 +19774,7 @@
           <t>OH Yeachan</t>
         </is>
       </c>
-      <c r="U330" t="inlineStr">
+      <c r="X330" t="inlineStr">
         <is>
           <t>42399</t>
         </is>
@@ -19802,7 +19832,7 @@
           <t>CHEN Fangjia</t>
         </is>
       </c>
-      <c r="U331" t="inlineStr">
+      <c r="X331" t="inlineStr">
         <is>
           <t>42638</t>
         </is>
@@ -19860,7 +19890,7 @@
           <t>WEWEGE Donovan</t>
         </is>
       </c>
-      <c r="U332" t="inlineStr">
+      <c r="X332" t="inlineStr">
         <is>
           <t>39241</t>
         </is>
@@ -19971,7 +20001,7 @@
           <t>DOMENJO Jordi</t>
         </is>
       </c>
-      <c r="U334" t="inlineStr">
+      <c r="X334" t="inlineStr">
         <is>
           <t>35739</t>
         </is>
@@ -20029,7 +20059,7 @@
           <t>THWAITE James</t>
         </is>
       </c>
-      <c r="U335" t="inlineStr">
+      <c r="X335" t="inlineStr">
         <is>
           <t>51862</t>
         </is>
@@ -20087,7 +20117,7 @@
           <t>LIU Chin-Han</t>
         </is>
       </c>
-      <c r="U336" t="inlineStr">
+      <c r="X336" t="inlineStr">
         <is>
           <t>51894</t>
         </is>
@@ -20145,7 +20175,7 @@
           <t>DEMIRCI Ismail</t>
         </is>
       </c>
-      <c r="U337" t="inlineStr">
+      <c r="X337" t="inlineStr">
         <is>
           <t>39914</t>
         </is>
@@ -20203,7 +20233,7 @@
           <t>CHAIDET Yutthakan</t>
         </is>
       </c>
-      <c r="U338" t="inlineStr">
+      <c r="X338" t="inlineStr">
         <is>
           <t>51798</t>
         </is>
@@ -20314,7 +20344,7 @@
           <t>SASAKI Shota</t>
         </is>
       </c>
-      <c r="U340" t="inlineStr">
+      <c r="X340" t="inlineStr">
         <is>
           <t>41610</t>
         </is>
@@ -20372,7 +20402,7 @@
           <t>HIGGINS Shaun</t>
         </is>
       </c>
-      <c r="U341" t="inlineStr">
+      <c r="X341" t="inlineStr">
         <is>
           <t>36655</t>
         </is>
@@ -20430,7 +20460,7 @@
           <t>SILVA Jose</t>
         </is>
       </c>
-      <c r="U342" t="inlineStr">
+      <c r="X342" t="inlineStr">
         <is>
           <t>36494</t>
         </is>
@@ -20541,7 +20571,7 @@
           <t>SERRA Thiago</t>
         </is>
       </c>
-      <c r="U344" t="inlineStr">
+      <c r="X344" t="inlineStr">
         <is>
           <t>41647</t>
         </is>
@@ -20599,7 +20629,7 @@
           <t>BOURHIS Jean Pierre</t>
         </is>
       </c>
-      <c r="U345" t="inlineStr">
+      <c r="X345" t="inlineStr">
         <is>
           <t>36968</t>
         </is>
@@ -20710,7 +20740,7 @@
           <t>GIBB Benjamin</t>
         </is>
       </c>
-      <c r="U347" t="inlineStr">
+      <c r="X347" t="inlineStr">
         <is>
           <t>36711</t>
         </is>
@@ -20768,7 +20798,7 @@
           <t>CURCEL Leonardo</t>
         </is>
       </c>
-      <c r="U348" t="inlineStr">
+      <c r="X348" t="inlineStr">
         <is>
           <t>38014</t>
         </is>
@@ -20826,7 +20856,7 @@
           <t>SZTUBA Igor</t>
         </is>
       </c>
-      <c r="U349" t="inlineStr">
+      <c r="X349" t="inlineStr">
         <is>
           <t>35087</t>
         </is>
@@ -20937,7 +20967,7 @@
           <t>HODSON Ethan</t>
         </is>
       </c>
-      <c r="U351" t="inlineStr">
+      <c r="X351" t="inlineStr">
         <is>
           <t>38437</t>
         </is>
@@ -20995,7 +21025,7 @@
           <t>JEGOU Liam</t>
         </is>
       </c>
-      <c r="U352" t="inlineStr">
+      <c r="X352" t="inlineStr">
         <is>
           <t>35820</t>
         </is>
@@ -21053,7 +21083,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U353" t="inlineStr">
+      <c r="X353" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -21111,7 +21141,7 @@
           <t>CECCON Paolo</t>
         </is>
       </c>
-      <c r="U354" t="inlineStr">
+      <c r="X354" t="inlineStr">
         <is>
           <t>39903</t>
         </is>
@@ -21169,7 +21199,7 @@
           <t>TRATSIAK Viktar</t>
         </is>
       </c>
-      <c r="U355" t="inlineStr">
+      <c r="X355" t="inlineStr">
         <is>
           <t>35270</t>
         </is>
@@ -21280,7 +21310,7 @@
           <t>ROSSI Sebastian</t>
         </is>
       </c>
-      <c r="U357" t="inlineStr">
+      <c r="X357" t="inlineStr">
         <is>
           <t>36915</t>
         </is>
@@ -21338,7 +21368,7 @@
           <t>GONDEK Kacper</t>
         </is>
       </c>
-      <c r="U358" t="inlineStr">
+      <c r="X358" t="inlineStr">
         <is>
           <t>35472</t>
         </is>
@@ -21396,7 +21426,7 @@
           <t>ERGUIN Jon</t>
         </is>
       </c>
-      <c r="U359" t="inlineStr">
+      <c r="X359" t="inlineStr">
         <is>
           <t>35740</t>
         </is>
@@ -21454,7 +21484,7 @@
           <t>TSAKMAKIS Christos</t>
         </is>
       </c>
-      <c r="U360" t="inlineStr">
+      <c r="X360" t="inlineStr">
         <is>
           <t>35433</t>
         </is>
@@ -21512,7 +21542,7 @@
           <t>JANE Michal</t>
         </is>
       </c>
-      <c r="U361" t="inlineStr">
+      <c r="X361" t="inlineStr">
         <is>
           <t>35059</t>
         </is>
@@ -21570,7 +21600,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U362" t="inlineStr">
+      <c r="X362" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -21628,7 +21658,7 @@
           <t>COLAZINGARI Roberto</t>
         </is>
       </c>
-      <c r="U363" t="inlineStr">
+      <c r="X363" t="inlineStr">
         <is>
           <t>35223</t>
         </is>
@@ -21686,7 +21716,7 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U364" t="inlineStr">
+      <c r="X364" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -21744,7 +21774,7 @@
           <t>MARINIC Matija</t>
         </is>
       </c>
-      <c r="U365" t="inlineStr">
+      <c r="X365" t="inlineStr">
         <is>
           <t>35595</t>
         </is>
@@ -21802,7 +21832,7 @@
           <t>CIPRESSI Stefano</t>
         </is>
       </c>
-      <c r="U366" t="inlineStr">
+      <c r="X366" t="inlineStr">
         <is>
           <t>35495</t>
         </is>
@@ -21860,7 +21890,7 @@
           <t>RAK Tomas</t>
         </is>
       </c>
-      <c r="U367" t="inlineStr">
+      <c r="X367" t="inlineStr">
         <is>
           <t>35056</t>
         </is>
@@ -21918,7 +21948,7 @@
           <t>LENARCIC Jure</t>
         </is>
       </c>
-      <c r="U368" t="inlineStr">
+      <c r="X368" t="inlineStr">
         <is>
           <t>36259</t>
         </is>
@@ -21976,7 +22006,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U369" t="inlineStr">
+      <c r="X369" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -22034,7 +22064,7 @@
           <t>O'FERRALL Caoimhe</t>
         </is>
       </c>
-      <c r="U370" t="inlineStr">
+      <c r="X370" t="inlineStr">
         <is>
           <t>61007</t>
         </is>
@@ -22145,7 +22175,7 @@
           <t>YAGI Airi</t>
         </is>
       </c>
-      <c r="U372" t="inlineStr">
+      <c r="X372" t="inlineStr">
         <is>
           <t>37756</t>
         </is>
@@ -22203,7 +22233,7 @@
           <t>CHEN Wei-Han</t>
         </is>
       </c>
-      <c r="U373" t="inlineStr">
+      <c r="X373" t="inlineStr">
         <is>
           <t>61630</t>
         </is>
@@ -22261,7 +22291,7 @@
           <t>KUBBE Kira</t>
         </is>
       </c>
-      <c r="U374" t="inlineStr">
+      <c r="X374" t="inlineStr">
         <is>
           <t>43464</t>
         </is>
@@ -22319,7 +22349,7 @@
           <t>SATO Ayano</t>
         </is>
       </c>
-      <c r="U375" t="inlineStr">
+      <c r="X375" t="inlineStr">
         <is>
           <t>60374</t>
         </is>
@@ -22377,7 +22407,7 @@
           <t>MURZINA Juta</t>
         </is>
       </c>
-      <c r="U376" t="inlineStr">
+      <c r="X376" t="inlineStr">
         <is>
           <t>39930</t>
         </is>
@@ -22435,7 +22465,7 @@
           <t>HERZOG Andrea</t>
         </is>
       </c>
-      <c r="U377" t="inlineStr">
+      <c r="X377" t="inlineStr">
         <is>
           <t>55099</t>
         </is>
@@ -22493,7 +22523,7 @@
           <t>MUKHGALEEVA Polina</t>
         </is>
       </c>
-      <c r="U378" t="inlineStr">
+      <c r="X378" t="inlineStr">
         <is>
           <t>35768</t>
         </is>
@@ -22551,7 +22581,7 @@
           <t>DUANGLAHWA Atcharaporn</t>
         </is>
       </c>
-      <c r="U379" t="inlineStr">
+      <c r="X379" t="inlineStr">
         <is>
           <t>61799</t>
         </is>
@@ -22662,7 +22692,7 @@
           <t>BIZJAK Nina</t>
         </is>
       </c>
-      <c r="U381" t="inlineStr">
+      <c r="X381" t="inlineStr">
         <is>
           <t>39984</t>
         </is>
@@ -22720,7 +22750,7 @@
           <t>TRAVERS Kelly</t>
         </is>
       </c>
-      <c r="U382" t="inlineStr">
+      <c r="X382" t="inlineStr">
         <is>
           <t>51643</t>
         </is>
@@ -22778,7 +22808,7 @@
           <t>DANIELS Haley</t>
         </is>
       </c>
-      <c r="U383" t="inlineStr">
+      <c r="X383" t="inlineStr">
         <is>
           <t>36260</t>
         </is>
@@ -22836,7 +22866,7 @@
           <t>JANCZY Justyna</t>
         </is>
       </c>
-      <c r="U384" t="inlineStr">
+      <c r="X384" t="inlineStr">
         <is>
           <t>43975</t>
         </is>
@@ -22894,7 +22924,7 @@
           <t>SABITOVA Zulfia</t>
         </is>
       </c>
-      <c r="U385" t="inlineStr">
+      <c r="X385" t="inlineStr">
         <is>
           <t>40572</t>
         </is>
@@ -22952,7 +22982,7 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U386" t="inlineStr">
+      <c r="X386" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -23010,7 +23040,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U387" t="inlineStr">
+      <c r="X387" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -23068,7 +23098,7 @@
           <t>VAN DER KNIJFF Annebel</t>
         </is>
       </c>
-      <c r="U388" t="inlineStr">
+      <c r="X388" t="inlineStr">
         <is>
           <t>39945</t>
         </is>
@@ -23126,7 +23156,7 @@
           <t>DOBROTVORSKA Viktoriia</t>
         </is>
       </c>
-      <c r="U389" t="inlineStr">
+      <c r="X389" t="inlineStr">
         <is>
           <t>35526</t>
         </is>
@@ -23184,7 +23214,7 @@
           <t>STOECKLIN Lena</t>
         </is>
       </c>
-      <c r="U390" t="inlineStr">
+      <c r="X390" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
@@ -23242,7 +23272,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U391" t="inlineStr">
+      <c r="X391" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -23300,7 +23330,7 @@
           <t>JANCOVA Monika</t>
         </is>
       </c>
-      <c r="U392" t="inlineStr">
+      <c r="X392" t="inlineStr">
         <is>
           <t>36015</t>
         </is>
@@ -23507,7 +23537,7 @@
           <t>BOURHIS Yves</t>
         </is>
       </c>
-      <c r="U396" t="inlineStr">
+      <c r="X396" t="inlineStr">
         <is>
           <t>63237</t>
         </is>
@@ -23565,7 +23595,7 @@
           <t>YAZAWA Kazuki</t>
         </is>
       </c>
-      <c r="U397" t="inlineStr">
+      <c r="X397" t="inlineStr">
         <is>
           <t>36482</t>
         </is>
@@ -23623,7 +23653,7 @@
           <t>LAUNAY Damien</t>
         </is>
       </c>
-      <c r="U398" t="inlineStr">
+      <c r="X398" t="inlineStr">
         <is>
           <t>60047</t>
         </is>
@@ -23681,7 +23711,7 @@
           <t>SANDVIK Dag</t>
         </is>
       </c>
-      <c r="U399" t="inlineStr">
+      <c r="X399" t="inlineStr">
         <is>
           <t>61587</t>
         </is>
@@ -23739,7 +23769,7 @@
           <t>MAHLABA Katleho</t>
         </is>
       </c>
-      <c r="U400" t="inlineStr">
+      <c r="X400" t="inlineStr">
         <is>
           <t>41574</t>
         </is>
@@ -23797,7 +23827,7 @@
           <t>LEE Dongheon</t>
         </is>
       </c>
-      <c r="U401" t="inlineStr">
+      <c r="X401" t="inlineStr">
         <is>
           <t>64855</t>
         </is>
@@ -23855,7 +23885,7 @@
           <t>SASAKI Tsubasa Terry</t>
         </is>
       </c>
-      <c r="U402" t="inlineStr">
+      <c r="X402" t="inlineStr">
         <is>
           <t>47085</t>
         </is>
@@ -23913,7 +23943,7 @@
           <t>SNIOKA Justinas</t>
         </is>
       </c>
-      <c r="U403" t="inlineStr">
+      <c r="X403" t="inlineStr">
         <is>
           <t>42915</t>
         </is>
@@ -23971,7 +24001,7 @@
           <t>AMIN Julianda</t>
         </is>
       </c>
-      <c r="U404" t="inlineStr">
+      <c r="X404" t="inlineStr">
         <is>
           <t>42154</t>
         </is>
@@ -24029,7 +24059,7 @@
           <t>MENDEZ Luis</t>
         </is>
       </c>
-      <c r="U405" t="inlineStr">
+      <c r="X405" t="inlineStr">
         <is>
           <t>41635</t>
         </is>
@@ -24087,7 +24117,7 @@
           <t>SPASIKJ Ljubomir</t>
         </is>
       </c>
-      <c r="U406" t="inlineStr">
+      <c r="X406" t="inlineStr">
         <is>
           <t>35591</t>
         </is>
@@ -24145,7 +24175,7 @@
           <t>VOLKOV Pyotr</t>
         </is>
       </c>
-      <c r="U407" t="inlineStr">
+      <c r="X407" t="inlineStr">
         <is>
           <t>39681</t>
         </is>
@@ -24203,7 +24233,7 @@
           <t>ABDUMUROTOV Tulkin</t>
         </is>
       </c>
-      <c r="U408" t="inlineStr">
+      <c r="X408" t="inlineStr">
         <is>
           <t>61160</t>
         </is>
@@ -24261,7 +24291,7 @@
           <t>AKINYEMI Johnathan</t>
         </is>
       </c>
-      <c r="U409" t="inlineStr">
+      <c r="X409" t="inlineStr">
         <is>
           <t>36822</t>
         </is>
@@ -24319,7 +24349,7 @@
           <t>ZHAO Zhengchao</t>
         </is>
       </c>
-      <c r="U410" t="inlineStr">
+      <c r="X410" t="inlineStr">
         <is>
           <t>63802</t>
         </is>
@@ -24377,7 +24407,7 @@
           <t>HUSSLEIN Hermann</t>
         </is>
       </c>
-      <c r="U411" t="inlineStr">
+      <c r="X411" t="inlineStr">
         <is>
           <t>35462</t>
         </is>
@@ -24435,7 +24465,7 @@
           <t>HASTINGS John</t>
         </is>
       </c>
-      <c r="U412" t="inlineStr">
+      <c r="X412" t="inlineStr">
         <is>
           <t>35540</t>
         </is>
@@ -24493,7 +24523,7 @@
           <t>NICHOLAS Bryden</t>
         </is>
       </c>
-      <c r="U413" t="inlineStr">
+      <c r="X413" t="inlineStr">
         <is>
           <t>36592</t>
         </is>
@@ -24551,7 +24581,7 @@
           <t>QUAN Xin</t>
         </is>
       </c>
-      <c r="U414" t="inlineStr">
+      <c r="X414" t="inlineStr">
         <is>
           <t>62343</t>
         </is>
@@ -24609,7 +24639,7 @@
           <t>LEE Jeong-Hyeon</t>
         </is>
       </c>
-      <c r="U415" t="inlineStr">
+      <c r="X415" t="inlineStr">
         <is>
           <t>42398</t>
         </is>
@@ -24667,7 +24697,7 @@
           <t>LEE Han-Cheng</t>
         </is>
       </c>
-      <c r="U416" t="inlineStr">
+      <c r="X416" t="inlineStr">
         <is>
           <t>39369</t>
         </is>
@@ -24725,7 +24755,7 @@
           <t>PROZHERIN Artem</t>
         </is>
       </c>
-      <c r="U417" t="inlineStr">
+      <c r="X417" t="inlineStr">
         <is>
           <t>35775</t>
         </is>
@@ -24783,7 +24813,7 @@
           <t>TUIRAVIRAVI Daniel</t>
         </is>
       </c>
-      <c r="U418" t="inlineStr">
+      <c r="X418" t="inlineStr">
         <is>
           <t>51998</t>
         </is>
@@ -24841,7 +24871,7 @@
           <t>CESPEDES PEREZ Arnaldo</t>
         </is>
       </c>
-      <c r="U419" t="inlineStr">
+      <c r="X419" t="inlineStr">
         <is>
           <t>41634</t>
         </is>
@@ -24899,7 +24929,7 @@
           <t>ZINOVYEV Pavel</t>
         </is>
       </c>
-      <c r="U420" t="inlineStr">
+      <c r="X420" t="inlineStr">
         <is>
           <t>39682</t>
         </is>
@@ -24957,7 +24987,7 @@
           <t>WAHLEN Fredrik</t>
         </is>
       </c>
-      <c r="U421" t="inlineStr">
+      <c r="X421" t="inlineStr">
         <is>
           <t>35102</t>
         </is>
@@ -25015,7 +25045,7 @@
           <t>SONG Min Hyeong</t>
         </is>
       </c>
-      <c r="U422" t="inlineStr">
+      <c r="X422" t="inlineStr">
         <is>
           <t>42400</t>
         </is>
@@ -25073,7 +25103,7 @@
           <t>RASIMAVICIUS Vilius</t>
         </is>
       </c>
-      <c r="U423" t="inlineStr">
+      <c r="X423" t="inlineStr">
         <is>
           <t>36965</t>
         </is>
@@ -25131,7 +25161,7 @@
           <t>DAVIDSON Elliott</t>
         </is>
       </c>
-      <c r="U424" t="inlineStr">
+      <c r="X424" t="inlineStr">
         <is>
           <t>43077</t>
         </is>
@@ -25189,7 +25219,7 @@
           <t>RYAN Cade</t>
         </is>
       </c>
-      <c r="U425" t="inlineStr">
+      <c r="X425" t="inlineStr">
         <is>
           <t>37919</t>
         </is>
@@ -25247,7 +25277,7 @@
           <t>BOURHIS Jean Pierre</t>
         </is>
       </c>
-      <c r="U426" t="inlineStr">
+      <c r="X426" t="inlineStr">
         <is>
           <t>36968</t>
         </is>
@@ -25305,7 +25335,7 @@
           <t>ACAR Anil</t>
         </is>
       </c>
-      <c r="U427" t="inlineStr">
+      <c r="X427" t="inlineStr">
         <is>
           <t>39900</t>
         </is>
@@ -25363,7 +25393,7 @@
           <t>PEREZ Alexis</t>
         </is>
       </c>
-      <c r="U428" t="inlineStr">
+      <c r="X428" t="inlineStr">
         <is>
           <t>41649</t>
         </is>
@@ -25421,7 +25451,7 @@
           <t>WEWEGE Donovan</t>
         </is>
       </c>
-      <c r="U429" t="inlineStr">
+      <c r="X429" t="inlineStr">
         <is>
           <t>39241</t>
         </is>
@@ -25479,7 +25509,7 @@
           <t>PAN Hung-Ming</t>
         </is>
       </c>
-      <c r="U430" t="inlineStr">
+      <c r="X430" t="inlineStr">
         <is>
           <t>37001</t>
         </is>
@@ -25537,7 +25567,7 @@
           <t>HELLARD Luc Suworna</t>
         </is>
       </c>
-      <c r="U431" t="inlineStr">
+      <c r="X431" t="inlineStr">
         <is>
           <t>43088</t>
         </is>
@@ -25595,7 +25625,7 @@
           <t>ATMANAVICIUS Mantas</t>
         </is>
       </c>
-      <c r="U432" t="inlineStr">
+      <c r="X432" t="inlineStr">
         <is>
           <t>35619</t>
         </is>
@@ -25653,7 +25683,7 @@
           <t>CURTIS Samuel</t>
         </is>
       </c>
-      <c r="U433" t="inlineStr">
+      <c r="X433" t="inlineStr">
         <is>
           <t>36683</t>
         </is>
@@ -25711,7 +25741,7 @@
           <t>ROSSI Lucas</t>
         </is>
       </c>
-      <c r="U434" t="inlineStr">
+      <c r="X434" t="inlineStr">
         <is>
           <t>36925</t>
         </is>
@@ -25769,7 +25799,7 @@
           <t>RODRIGUES Fabio</t>
         </is>
       </c>
-      <c r="U435" t="inlineStr">
+      <c r="X435" t="inlineStr">
         <is>
           <t>38023</t>
         </is>
@@ -25827,7 +25857,7 @@
           <t>ROUICH Mehdi</t>
         </is>
       </c>
-      <c r="U436" t="inlineStr">
+      <c r="X436" t="inlineStr">
         <is>
           <t>36944</t>
         </is>
@@ -25885,7 +25915,7 @@
           <t>TAN Ya</t>
         </is>
       </c>
-      <c r="U437" t="inlineStr">
+      <c r="X437" t="inlineStr">
         <is>
           <t>52024</t>
         </is>
@@ -25943,7 +25973,7 @@
           <t>TEUNISSEN Marnix</t>
         </is>
       </c>
-      <c r="U438" t="inlineStr">
+      <c r="X438" t="inlineStr">
         <is>
           <t>35695</t>
         </is>
@@ -26001,7 +26031,7 @@
           <t>MARTINS TAQUES Ricardo</t>
         </is>
       </c>
-      <c r="U439" t="inlineStr">
+      <c r="X439" t="inlineStr">
         <is>
           <t>38022</t>
         </is>
@@ -26059,7 +26089,7 @@
           <t>CORDERO Matias</t>
         </is>
       </c>
-      <c r="U440" t="inlineStr">
+      <c r="X440" t="inlineStr">
         <is>
           <t>36918</t>
         </is>
@@ -26170,7 +26200,7 @@
           <t>SEKER Enzo</t>
         </is>
       </c>
-      <c r="U442" t="inlineStr">
+      <c r="X442" t="inlineStr">
         <is>
           <t>39917</t>
         </is>
@@ -26228,7 +26258,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U443" t="inlineStr">
+      <c r="X443" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -26286,7 +26316,7 @@
           <t>KARAMARKO Filip</t>
         </is>
       </c>
-      <c r="U444" t="inlineStr">
+      <c r="X444" t="inlineStr">
         <is>
           <t>35596</t>
         </is>
@@ -26344,7 +26374,7 @@
           <t>HOLMER Erik</t>
         </is>
       </c>
-      <c r="U445" t="inlineStr">
+      <c r="X445" t="inlineStr">
         <is>
           <t>35104</t>
         </is>
@@ -26402,7 +26432,7 @@
           <t>MANN Aaron</t>
         </is>
       </c>
-      <c r="U446" t="inlineStr">
+      <c r="X446" t="inlineStr">
         <is>
           <t>39898</t>
         </is>
@@ -26460,7 +26490,7 @@
           <t>TSVIET Igor</t>
         </is>
       </c>
-      <c r="U447" t="inlineStr">
+      <c r="X447" t="inlineStr">
         <is>
           <t>35527</t>
         </is>
@@ -26518,7 +26548,7 @@
           <t>SILVA Ivan</t>
         </is>
       </c>
-      <c r="U448" t="inlineStr">
+      <c r="X448" t="inlineStr">
         <is>
           <t>35482</t>
         </is>
@@ -26576,7 +26606,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U449" t="inlineStr">
+      <c r="X449" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -26634,7 +26664,7 @@
           <t>OSCHMAUTZ Felix</t>
         </is>
       </c>
-      <c r="U450" t="inlineStr">
+      <c r="X450" t="inlineStr">
         <is>
           <t>51856</t>
         </is>
@@ -26692,7 +26722,7 @@
           <t>MRKOCI Marko</t>
         </is>
       </c>
-      <c r="U451" t="inlineStr">
+      <c r="X451" t="inlineStr">
         <is>
           <t>35592</t>
         </is>
@@ -26750,7 +26780,7 @@
           <t>TAYLER Michael</t>
         </is>
       </c>
-      <c r="U452" t="inlineStr">
+      <c r="X452" t="inlineStr">
         <is>
           <t>36262</t>
         </is>
@@ -26808,7 +26838,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U453" t="inlineStr">
+      <c r="X453" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -26866,7 +26896,7 @@
           <t>DOUGOUD Martin</t>
         </is>
       </c>
-      <c r="U454" t="inlineStr">
+      <c r="X454" t="inlineStr">
         <is>
           <t>35426</t>
         </is>
@@ -26924,7 +26954,7 @@
           <t>ADACHI Kazuya</t>
         </is>
       </c>
-      <c r="U455" t="inlineStr">
+      <c r="X455" t="inlineStr">
         <is>
           <t>36646</t>
         </is>
@@ -26982,7 +27012,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U456" t="inlineStr">
+      <c r="X456" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -27040,7 +27070,7 @@
           <t>LEITNER Mario</t>
         </is>
       </c>
-      <c r="U457" t="inlineStr">
+      <c r="X457" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
@@ -27151,7 +27181,7 @@
           <t>FORBES-CRYANS Bradley</t>
         </is>
       </c>
-      <c r="U459" t="inlineStr">
+      <c r="X459" t="inlineStr">
         <is>
           <t>36513</t>
         </is>
@@ -27209,7 +27239,7 @@
           <t>MALEK Andrej</t>
         </is>
       </c>
-      <c r="U460" t="inlineStr">
+      <c r="X460" t="inlineStr">
         <is>
           <t>39246</t>
         </is>
@@ -27267,7 +27297,7 @@
           <t>OHRSTROM Isak</t>
         </is>
       </c>
-      <c r="U461" t="inlineStr">
+      <c r="X461" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
@@ -27325,7 +27355,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U462" t="inlineStr">
+      <c r="X462" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -27436,7 +27466,7 @@
           <t>WERRO Lukas</t>
         </is>
       </c>
-      <c r="U464" t="inlineStr">
+      <c r="X464" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
@@ -27494,7 +27524,7 @@
           <t>POWELL Richard</t>
         </is>
       </c>
-      <c r="U465" t="inlineStr">
+      <c r="X465" t="inlineStr">
         <is>
           <t>36444</t>
         </is>
@@ -27605,7 +27635,7 @@
           <t>OBLINGER Helmut</t>
         </is>
       </c>
-      <c r="U467" t="inlineStr">
+      <c r="X467" t="inlineStr">
         <is>
           <t>35281</t>
         </is>
@@ -27663,7 +27693,7 @@
           <t>OKREGLAK Maciej</t>
         </is>
       </c>
-      <c r="U468" t="inlineStr">
+      <c r="X468" t="inlineStr">
         <is>
           <t>35088</t>
         </is>
@@ -27774,7 +27804,7 @@
           <t>EIGEL Pavel</t>
         </is>
       </c>
-      <c r="U470" t="inlineStr">
+      <c r="X470" t="inlineStr">
         <is>
           <t>35458</t>
         </is>
@@ -27832,7 +27862,7 @@
           <t>MEGLIC Jure</t>
         </is>
       </c>
-      <c r="U471" t="inlineStr">
+      <c r="X471" t="inlineStr">
         <is>
           <t>35590</t>
         </is>
@@ -27890,7 +27920,7 @@
           <t>HAYWARD Ben</t>
         </is>
       </c>
-      <c r="U472" t="inlineStr">
+      <c r="X472" t="inlineStr">
         <is>
           <t>35539</t>
         </is>
@@ -28001,7 +28031,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U474" t="inlineStr">
+      <c r="X474" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -28059,7 +28089,7 @@
           <t>MOLMENTI Daniele</t>
         </is>
       </c>
-      <c r="U475" t="inlineStr">
+      <c r="X475" t="inlineStr">
         <is>
           <t>42017</t>
         </is>
@@ -28117,7 +28147,7 @@
           <t>BRUS Simon</t>
         </is>
       </c>
-      <c r="U476" t="inlineStr">
+      <c r="X476" t="inlineStr">
         <is>
           <t>39076</t>
         </is>
@@ -28175,7 +28205,7 @@
           <t>PETERLIN Janos</t>
         </is>
       </c>
-      <c r="U477" t="inlineStr">
+      <c r="X477" t="inlineStr">
         <is>
           <t>36268</t>
         </is>
@@ -28233,7 +28263,7 @@
           <t>DE GENNARO Giovanni</t>
         </is>
       </c>
-      <c r="U478" t="inlineStr">
+      <c r="X478" t="inlineStr">
         <is>
           <t>35244</t>
         </is>
@@ -28291,7 +28321,7 @@
           <t>KURT Michael</t>
         </is>
       </c>
-      <c r="U479" t="inlineStr">
+      <c r="X479" t="inlineStr">
         <is>
           <t>35346</t>
         </is>
@@ -28349,7 +28379,7 @@
           <t>ROMEO Andrea</t>
         </is>
       </c>
-      <c r="U480" t="inlineStr">
+      <c r="X480" t="inlineStr">
         <is>
           <t>35502</t>
         </is>
@@ -28407,7 +28437,7 @@
           <t>HALCIN Martin</t>
         </is>
       </c>
-      <c r="U481" t="inlineStr">
+      <c r="X481" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
@@ -28465,7 +28495,7 @@
           <t>CRESPO Joan</t>
         </is>
       </c>
-      <c r="U482" t="inlineStr">
+      <c r="X482" t="inlineStr">
         <is>
           <t>35749</t>
         </is>
@@ -28523,7 +28553,7 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U483" t="inlineStr">
+      <c r="X483" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -28581,7 +28611,7 @@
           <t>GRIMM Alexander</t>
         </is>
       </c>
-      <c r="U484" t="inlineStr">
+      <c r="X484" t="inlineStr">
         <is>
           <t>35112</t>
         </is>
@@ -28639,7 +28669,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U485" t="inlineStr">
+      <c r="X485" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -28697,7 +28727,7 @@
           <t>BERSINGER Thomas</t>
         </is>
       </c>
-      <c r="U486" t="inlineStr">
+      <c r="X486" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
@@ -28755,7 +28785,7 @@
           <t>CLARKE Joseph</t>
         </is>
       </c>
-      <c r="U487" t="inlineStr">
+      <c r="X487" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
@@ -28813,7 +28843,7 @@
           <t>DOBY Mathieu</t>
         </is>
       </c>
-      <c r="U488" t="inlineStr">
+      <c r="X488" t="inlineStr">
         <is>
           <t>35292</t>
         </is>
@@ -28871,7 +28901,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U489" t="inlineStr">
+      <c r="X489" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -28929,7 +28959,7 @@
           <t>COMBOT Sebastien</t>
         </is>
       </c>
-      <c r="U490" t="inlineStr">
+      <c r="X490" t="inlineStr">
         <is>
           <t>35234</t>
         </is>
@@ -28987,7 +29017,7 @@
           <t>HERNANZ Samuel</t>
         </is>
       </c>
-      <c r="U491" t="inlineStr">
+      <c r="X491" t="inlineStr">
         <is>
           <t>35786</t>
         </is>
@@ -29045,7 +29075,7 @@
           <t>AIGNER Hannes</t>
         </is>
       </c>
-      <c r="U492" t="inlineStr">
+      <c r="X492" t="inlineStr">
         <is>
           <t>35115</t>
         </is>
@@ -29103,7 +29133,7 @@
           <t>BIAZIZZO Mathieu</t>
         </is>
       </c>
-      <c r="U493" t="inlineStr">
+      <c r="X493" t="inlineStr">
         <is>
           <t>35484</t>
         </is>
@@ -29161,7 +29191,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U494" t="inlineStr">
+      <c r="X494" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -29219,7 +29249,7 @@
           <t>POLACZYK Mateusz</t>
         </is>
       </c>
-      <c r="U495" t="inlineStr">
+      <c r="X495" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
@@ -29277,7 +29307,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U496" t="inlineStr">
+      <c r="X496" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -29335,7 +29365,7 @@
           <t>SCHUBERT Sebastian</t>
         </is>
       </c>
-      <c r="U497" t="inlineStr">
+      <c r="X497" t="inlineStr">
         <is>
           <t>35114</t>
         </is>
@@ -29393,7 +29423,7 @@
           <t>NEVEU Boris</t>
         </is>
       </c>
-      <c r="U498" t="inlineStr">
+      <c r="X498" t="inlineStr">
         <is>
           <t>35396</t>
         </is>
@@ -29504,7 +29534,7 @@
           <t>BOURHIS Yves</t>
         </is>
       </c>
-      <c r="U500" t="inlineStr">
+      <c r="X500" t="inlineStr">
         <is>
           <t>63237</t>
         </is>
@@ -29562,7 +29592,7 @@
           <t>YAZAWA Kazuki</t>
         </is>
       </c>
-      <c r="U501" t="inlineStr">
+      <c r="X501" t="inlineStr">
         <is>
           <t>36482</t>
         </is>
@@ -29620,7 +29650,7 @@
           <t>LAUNAY Damien</t>
         </is>
       </c>
-      <c r="U502" t="inlineStr">
+      <c r="X502" t="inlineStr">
         <is>
           <t>60047</t>
         </is>
@@ -29678,7 +29708,7 @@
           <t>SANDVIK Dag</t>
         </is>
       </c>
-      <c r="U503" t="inlineStr">
+      <c r="X503" t="inlineStr">
         <is>
           <t>61587</t>
         </is>
@@ -29736,7 +29766,7 @@
           <t>MAHLABA Katleho</t>
         </is>
       </c>
-      <c r="U504" t="inlineStr">
+      <c r="X504" t="inlineStr">
         <is>
           <t>41574</t>
         </is>
@@ -29794,7 +29824,7 @@
           <t>LEE Dongheon</t>
         </is>
       </c>
-      <c r="U505" t="inlineStr">
+      <c r="X505" t="inlineStr">
         <is>
           <t>64855</t>
         </is>
@@ -29852,7 +29882,7 @@
           <t>SASAKI Tsubasa Terry</t>
         </is>
       </c>
-      <c r="U506" t="inlineStr">
+      <c r="X506" t="inlineStr">
         <is>
           <t>47085</t>
         </is>
@@ -29910,7 +29940,7 @@
           <t>SNIOKA Justinas</t>
         </is>
       </c>
-      <c r="U507" t="inlineStr">
+      <c r="X507" t="inlineStr">
         <is>
           <t>42915</t>
         </is>
@@ -29968,7 +29998,7 @@
           <t>AMIN Julianda</t>
         </is>
       </c>
-      <c r="U508" t="inlineStr">
+      <c r="X508" t="inlineStr">
         <is>
           <t>42154</t>
         </is>
@@ -30026,7 +30056,7 @@
           <t>MENDEZ Luis</t>
         </is>
       </c>
-      <c r="U509" t="inlineStr">
+      <c r="X509" t="inlineStr">
         <is>
           <t>41635</t>
         </is>
@@ -30084,7 +30114,7 @@
           <t>SPASIKJ Ljubomir</t>
         </is>
       </c>
-      <c r="U510" t="inlineStr">
+      <c r="X510" t="inlineStr">
         <is>
           <t>35591</t>
         </is>
@@ -30142,7 +30172,7 @@
           <t>VOLKOV Pyotr</t>
         </is>
       </c>
-      <c r="U511" t="inlineStr">
+      <c r="X511" t="inlineStr">
         <is>
           <t>39681</t>
         </is>
@@ -30200,7 +30230,7 @@
           <t>ABDUMUROTOV Tulkin</t>
         </is>
       </c>
-      <c r="U512" t="inlineStr">
+      <c r="X512" t="inlineStr">
         <is>
           <t>61160</t>
         </is>
@@ -30258,7 +30288,7 @@
           <t>AKINYEMI Johnathan</t>
         </is>
       </c>
-      <c r="U513" t="inlineStr">
+      <c r="X513" t="inlineStr">
         <is>
           <t>36822</t>
         </is>
@@ -30316,7 +30346,7 @@
           <t>ZHAO Zhengchao</t>
         </is>
       </c>
-      <c r="U514" t="inlineStr">
+      <c r="X514" t="inlineStr">
         <is>
           <t>63802</t>
         </is>
@@ -30374,7 +30404,7 @@
           <t>HUSSLEIN Hermann</t>
         </is>
       </c>
-      <c r="U515" t="inlineStr">
+      <c r="X515" t="inlineStr">
         <is>
           <t>35462</t>
         </is>
@@ -30432,7 +30462,7 @@
           <t>HASTINGS John</t>
         </is>
       </c>
-      <c r="U516" t="inlineStr">
+      <c r="X516" t="inlineStr">
         <is>
           <t>35540</t>
         </is>
@@ -30490,7 +30520,7 @@
           <t>NICHOLAS Bryden</t>
         </is>
       </c>
-      <c r="U517" t="inlineStr">
+      <c r="X517" t="inlineStr">
         <is>
           <t>36592</t>
         </is>
@@ -30548,7 +30578,7 @@
           <t>QUAN Xin</t>
         </is>
       </c>
-      <c r="U518" t="inlineStr">
+      <c r="X518" t="inlineStr">
         <is>
           <t>62343</t>
         </is>
@@ -30606,7 +30636,7 @@
           <t>LEE Jeong-Hyeon</t>
         </is>
       </c>
-      <c r="U519" t="inlineStr">
+      <c r="X519" t="inlineStr">
         <is>
           <t>42398</t>
         </is>
@@ -30664,7 +30694,7 @@
           <t>LEE Han-Cheng</t>
         </is>
       </c>
-      <c r="U520" t="inlineStr">
+      <c r="X520" t="inlineStr">
         <is>
           <t>39369</t>
         </is>
@@ -30722,7 +30752,7 @@
           <t>PROZHERIN Artem</t>
         </is>
       </c>
-      <c r="U521" t="inlineStr">
+      <c r="X521" t="inlineStr">
         <is>
           <t>35775</t>
         </is>
@@ -30780,7 +30810,7 @@
           <t>TUIRAVIRAVI Daniel</t>
         </is>
       </c>
-      <c r="U522" t="inlineStr">
+      <c r="X522" t="inlineStr">
         <is>
           <t>51998</t>
         </is>
@@ -30838,7 +30868,7 @@
           <t>CESPEDES PEREZ Arnaldo</t>
         </is>
       </c>
-      <c r="U523" t="inlineStr">
+      <c r="X523" t="inlineStr">
         <is>
           <t>41634</t>
         </is>
@@ -30896,7 +30926,7 @@
           <t>ZINOVYEV Pavel</t>
         </is>
       </c>
-      <c r="U524" t="inlineStr">
+      <c r="X524" t="inlineStr">
         <is>
           <t>39682</t>
         </is>
@@ -30954,7 +30984,7 @@
           <t>WAHLEN Fredrik</t>
         </is>
       </c>
-      <c r="U525" t="inlineStr">
+      <c r="X525" t="inlineStr">
         <is>
           <t>35102</t>
         </is>
@@ -31012,7 +31042,7 @@
           <t>SONG Min Hyeong</t>
         </is>
       </c>
-      <c r="U526" t="inlineStr">
+      <c r="X526" t="inlineStr">
         <is>
           <t>42400</t>
         </is>
@@ -31070,7 +31100,7 @@
           <t>RASIMAVICIUS Vilius</t>
         </is>
       </c>
-      <c r="U527" t="inlineStr">
+      <c r="X527" t="inlineStr">
         <is>
           <t>36965</t>
         </is>
@@ -31128,7 +31158,7 @@
           <t>DAVIDSON Elliott</t>
         </is>
       </c>
-      <c r="U528" t="inlineStr">
+      <c r="X528" t="inlineStr">
         <is>
           <t>43077</t>
         </is>
@@ -31186,7 +31216,7 @@
           <t>RYAN Cade</t>
         </is>
       </c>
-      <c r="U529" t="inlineStr">
+      <c r="X529" t="inlineStr">
         <is>
           <t>37919</t>
         </is>
@@ -31244,7 +31274,7 @@
           <t>BOURHIS Jean Pierre</t>
         </is>
       </c>
-      <c r="U530" t="inlineStr">
+      <c r="X530" t="inlineStr">
         <is>
           <t>36968</t>
         </is>
@@ -31302,7 +31332,7 @@
           <t>ACAR Anil</t>
         </is>
       </c>
-      <c r="U531" t="inlineStr">
+      <c r="X531" t="inlineStr">
         <is>
           <t>39900</t>
         </is>
@@ -31360,7 +31390,7 @@
           <t>PEREZ Alexis</t>
         </is>
       </c>
-      <c r="U532" t="inlineStr">
+      <c r="X532" t="inlineStr">
         <is>
           <t>41649</t>
         </is>
@@ -31418,7 +31448,7 @@
           <t>WEWEGE Donovan</t>
         </is>
       </c>
-      <c r="U533" t="inlineStr">
+      <c r="X533" t="inlineStr">
         <is>
           <t>39241</t>
         </is>
@@ -31476,7 +31506,7 @@
           <t>PAN Hung-Ming</t>
         </is>
       </c>
-      <c r="U534" t="inlineStr">
+      <c r="X534" t="inlineStr">
         <is>
           <t>37001</t>
         </is>
@@ -31534,7 +31564,7 @@
           <t>HELLARD Luc Suworna</t>
         </is>
       </c>
-      <c r="U535" t="inlineStr">
+      <c r="X535" t="inlineStr">
         <is>
           <t>43088</t>
         </is>
@@ -31592,7 +31622,7 @@
           <t>ATMANAVICIUS Mantas</t>
         </is>
       </c>
-      <c r="U536" t="inlineStr">
+      <c r="X536" t="inlineStr">
         <is>
           <t>35619</t>
         </is>
@@ -31650,7 +31680,7 @@
           <t>CURTIS Samuel</t>
         </is>
       </c>
-      <c r="U537" t="inlineStr">
+      <c r="X537" t="inlineStr">
         <is>
           <t>36683</t>
         </is>
@@ -31708,7 +31738,7 @@
           <t>ROSSI Lucas</t>
         </is>
       </c>
-      <c r="U538" t="inlineStr">
+      <c r="X538" t="inlineStr">
         <is>
           <t>36925</t>
         </is>
@@ -31766,7 +31796,7 @@
           <t>RODRIGUES Fabio</t>
         </is>
       </c>
-      <c r="U539" t="inlineStr">
+      <c r="X539" t="inlineStr">
         <is>
           <t>38023</t>
         </is>
@@ -31824,7 +31854,7 @@
           <t>ROUICH Mehdi</t>
         </is>
       </c>
-      <c r="U540" t="inlineStr">
+      <c r="X540" t="inlineStr">
         <is>
           <t>36944</t>
         </is>
@@ -31882,7 +31912,7 @@
           <t>TEUNISSEN Marnix</t>
         </is>
       </c>
-      <c r="U541" t="inlineStr">
+      <c r="X541" t="inlineStr">
         <is>
           <t>35695</t>
         </is>
@@ -31940,7 +31970,7 @@
           <t>MARTINS TAQUES Ricardo</t>
         </is>
       </c>
-      <c r="U542" t="inlineStr">
+      <c r="X542" t="inlineStr">
         <is>
           <t>38022</t>
         </is>
@@ -31998,7 +32028,7 @@
           <t>CORDERO Matias</t>
         </is>
       </c>
-      <c r="U543" t="inlineStr">
+      <c r="X543" t="inlineStr">
         <is>
           <t>36918</t>
         </is>
@@ -32109,7 +32139,7 @@
           <t>SEKER Enzo</t>
         </is>
       </c>
-      <c r="U545" t="inlineStr">
+      <c r="X545" t="inlineStr">
         <is>
           <t>39917</t>
         </is>
@@ -32167,7 +32197,7 @@
           <t>NABASKUES Unai</t>
         </is>
       </c>
-      <c r="U546" t="inlineStr">
+      <c r="X546" t="inlineStr">
         <is>
           <t>38775</t>
         </is>
@@ -32225,7 +32255,7 @@
           <t>KARAMARKO Filip</t>
         </is>
       </c>
-      <c r="U547" t="inlineStr">
+      <c r="X547" t="inlineStr">
         <is>
           <t>35596</t>
         </is>
@@ -32283,7 +32313,7 @@
           <t>HOLMER Erik</t>
         </is>
       </c>
-      <c r="U548" t="inlineStr">
+      <c r="X548" t="inlineStr">
         <is>
           <t>35104</t>
         </is>
@@ -32341,7 +32371,7 @@
           <t>MANN Aaron</t>
         </is>
       </c>
-      <c r="U549" t="inlineStr">
+      <c r="X549" t="inlineStr">
         <is>
           <t>39898</t>
         </is>
@@ -32399,7 +32429,7 @@
           <t>TSVIET Igor</t>
         </is>
       </c>
-      <c r="U550" t="inlineStr">
+      <c r="X550" t="inlineStr">
         <is>
           <t>35527</t>
         </is>
@@ -32457,7 +32487,7 @@
           <t>SILVA Ivan</t>
         </is>
       </c>
-      <c r="U551" t="inlineStr">
+      <c r="X551" t="inlineStr">
         <is>
           <t>35482</t>
         </is>
@@ -32515,7 +32545,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U552" t="inlineStr">
+      <c r="X552" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -32573,7 +32603,7 @@
           <t>OSCHMAUTZ Felix</t>
         </is>
       </c>
-      <c r="U553" t="inlineStr">
+      <c r="X553" t="inlineStr">
         <is>
           <t>51856</t>
         </is>
@@ -32631,7 +32661,7 @@
           <t>MRKOCI Marko</t>
         </is>
       </c>
-      <c r="U554" t="inlineStr">
+      <c r="X554" t="inlineStr">
         <is>
           <t>35592</t>
         </is>
@@ -32689,7 +32719,7 @@
           <t>TAYLER Michael</t>
         </is>
       </c>
-      <c r="U555" t="inlineStr">
+      <c r="X555" t="inlineStr">
         <is>
           <t>36262</t>
         </is>
@@ -32747,7 +32777,7 @@
           <t>DOUGOUD Martin</t>
         </is>
       </c>
-      <c r="U556" t="inlineStr">
+      <c r="X556" t="inlineStr">
         <is>
           <t>35426</t>
         </is>
@@ -32805,7 +32835,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U557" t="inlineStr">
+      <c r="X557" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -32863,7 +32893,7 @@
           <t>LEITNER Mario</t>
         </is>
       </c>
-      <c r="U558" t="inlineStr">
+      <c r="X558" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
@@ -32974,7 +33004,7 @@
           <t>MALEK Andrej</t>
         </is>
       </c>
-      <c r="U560" t="inlineStr">
+      <c r="X560" t="inlineStr">
         <is>
           <t>39246</t>
         </is>
@@ -33032,7 +33062,7 @@
           <t>OHRSTROM Isak</t>
         </is>
       </c>
-      <c r="U561" t="inlineStr">
+      <c r="X561" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
@@ -33143,7 +33173,7 @@
           <t>WERRO Lukas</t>
         </is>
       </c>
-      <c r="U563" t="inlineStr">
+      <c r="X563" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
@@ -33201,7 +33231,7 @@
           <t>OBLINGER Helmut</t>
         </is>
       </c>
-      <c r="U564" t="inlineStr">
+      <c r="X564" t="inlineStr">
         <is>
           <t>35281</t>
         </is>
@@ -33259,7 +33289,7 @@
           <t>OKREGLAK Maciej</t>
         </is>
       </c>
-      <c r="U565" t="inlineStr">
+      <c r="X565" t="inlineStr">
         <is>
           <t>35088</t>
         </is>
@@ -33317,7 +33347,7 @@
           <t>HAYWARD Ben</t>
         </is>
       </c>
-      <c r="U566" t="inlineStr">
+      <c r="X566" t="inlineStr">
         <is>
           <t>35539</t>
         </is>
@@ -33375,7 +33405,7 @@
           <t>DE GENNARO Giovanni</t>
         </is>
       </c>
-      <c r="U567" t="inlineStr">
+      <c r="X567" t="inlineStr">
         <is>
           <t>35244</t>
         </is>
@@ -33433,7 +33463,7 @@
           <t>DOBY Mathieu</t>
         </is>
       </c>
-      <c r="U568" t="inlineStr">
+      <c r="X568" t="inlineStr">
         <is>
           <t>35292</t>
         </is>
@@ -33491,7 +33521,7 @@
           <t>HERNANZ Samuel</t>
         </is>
       </c>
-      <c r="U569" t="inlineStr">
+      <c r="X569" t="inlineStr">
         <is>
           <t>35786</t>
         </is>
@@ -33549,7 +33579,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U570" t="inlineStr">
+      <c r="X570" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -33607,7 +33637,7 @@
           <t>SCHUBERT Sebastian</t>
         </is>
       </c>
-      <c r="U571" t="inlineStr">
+      <c r="X571" t="inlineStr">
         <is>
           <t>35114</t>
         </is>
@@ -33665,7 +33695,7 @@
           <t>NEVEU Boris</t>
         </is>
       </c>
-      <c r="U572" t="inlineStr">
+      <c r="X572" t="inlineStr">
         <is>
           <t>35396</t>
         </is>
@@ -33920,12 +33950,12 @@
           <t>MAJERCZAK Grzegorz</t>
         </is>
       </c>
-      <c r="U577" t="inlineStr">
+      <c r="X577" t="inlineStr">
         <is>
           <t>35085</t>
         </is>
       </c>
-      <c r="V577" t="inlineStr">
+      <c r="Y577" t="inlineStr">
         <is>
           <t>35086</t>
         </is>
@@ -33988,12 +34018,12 @@
           <t>USHAKOV Artem</t>
         </is>
       </c>
-      <c r="U578" t="inlineStr">
+      <c r="X578" t="inlineStr">
         <is>
           <t>35454</t>
         </is>
       </c>
-      <c r="V578" t="inlineStr">
+      <c r="Y578" t="inlineStr">
         <is>
           <t>35455</t>
         </is>
@@ -34056,7 +34086,7 @@
           <t>PITT Greg</t>
         </is>
       </c>
-      <c r="U579" t="inlineStr">
+      <c r="X579" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -34119,12 +34149,12 @@
           <t>CHEN Jin</t>
         </is>
       </c>
-      <c r="U580" t="inlineStr">
+      <c r="X580" t="inlineStr">
         <is>
           <t>42237</t>
         </is>
       </c>
-      <c r="V580" t="inlineStr">
+      <c r="Y580" t="inlineStr">
         <is>
           <t>42238</t>
         </is>
@@ -34187,12 +34217,12 @@
           <t>MUELLER Kevin</t>
         </is>
       </c>
-      <c r="U581" t="inlineStr">
+      <c r="X581" t="inlineStr">
         <is>
           <t>35148</t>
         </is>
       </c>
-      <c r="V581" t="inlineStr">
+      <c r="Y581" t="inlineStr">
         <is>
           <t>35149</t>
         </is>
@@ -34255,12 +34285,12 @@
           <t>POCHWALA Marcin</t>
         </is>
       </c>
-      <c r="U582" t="inlineStr">
+      <c r="X582" t="inlineStr">
         <is>
           <t>35080</t>
         </is>
       </c>
-      <c r="V582" t="inlineStr">
+      <c r="Y582" t="inlineStr">
         <is>
           <t>35079</t>
         </is>
@@ -34323,12 +34353,12 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="U583" t="inlineStr">
+      <c r="X583" t="inlineStr">
         <is>
           <t>35060</t>
         </is>
       </c>
-      <c r="V583" t="inlineStr">
+      <c r="Y583" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
@@ -34391,12 +34421,12 @@
           <t>FERRARI Niccolo</t>
         </is>
       </c>
-      <c r="U584" t="inlineStr">
+      <c r="X584" t="inlineStr">
         <is>
           <t>35497</t>
         </is>
       </c>
-      <c r="V584" t="inlineStr">
+      <c r="Y584" t="inlineStr">
         <is>
           <t>35498</t>
         </is>
@@ -34459,12 +34489,12 @@
           <t>LARIONOV Dmitry</t>
         </is>
       </c>
-      <c r="U585" t="inlineStr">
+      <c r="X585" t="inlineStr">
         <is>
           <t>35449</t>
         </is>
       </c>
-      <c r="V585" t="inlineStr">
+      <c r="Y585" t="inlineStr">
         <is>
           <t>35450</t>
         </is>
@@ -34527,12 +34557,12 @@
           <t>BENZIEN Jan</t>
         </is>
       </c>
-      <c r="U586" t="inlineStr">
+      <c r="X586" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
       </c>
-      <c r="V586" t="inlineStr">
+      <c r="Y586" t="inlineStr">
         <is>
           <t>35134</t>
         </is>
@@ -34595,12 +34625,12 @@
           <t>BRZEZINSKI Andrzej</t>
         </is>
       </c>
-      <c r="U587" t="inlineStr">
+      <c r="X587" t="inlineStr">
         <is>
           <t>35082</t>
         </is>
       </c>
-      <c r="V587" t="inlineStr">
+      <c r="Y587" t="inlineStr">
         <is>
           <t>35081</t>
         </is>
@@ -34663,12 +34693,12 @@
           <t>HOCHSCHORNER Peter</t>
         </is>
       </c>
-      <c r="U588" t="inlineStr">
+      <c r="X588" t="inlineStr">
         <is>
           <t>35356</t>
         </is>
       </c>
-      <c r="V588" t="inlineStr">
+      <c r="Y588" t="inlineStr">
         <is>
           <t>35357</t>
         </is>
@@ -34789,12 +34819,12 @@
           <t>BECKER Thomas</t>
         </is>
       </c>
-      <c r="U590" t="inlineStr">
+      <c r="X590" t="inlineStr">
         <is>
           <t>35139</t>
         </is>
       </c>
-      <c r="V590" t="inlineStr">
+      <c r="Y590" t="inlineStr">
         <is>
           <t>35143</t>
         </is>
@@ -34857,12 +34887,12 @@
           <t>SINDLER Marek</t>
         </is>
       </c>
-      <c r="U591" t="inlineStr">
+      <c r="X591" t="inlineStr">
         <is>
           <t>35062</t>
         </is>
       </c>
-      <c r="V591" t="inlineStr">
+      <c r="Y591" t="inlineStr">
         <is>
           <t>35063</t>
         </is>
@@ -34925,12 +34955,12 @@
           <t>TALJAT Saso</t>
         </is>
       </c>
-      <c r="U592" t="inlineStr">
+      <c r="X592" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
       </c>
-      <c r="V592" t="inlineStr">
+      <c r="Y592" t="inlineStr">
         <is>
           <t>36270</t>
         </is>
@@ -34993,12 +35023,12 @@
           <t>SKANTAR Peter</t>
         </is>
       </c>
-      <c r="U593" t="inlineStr">
+      <c r="X593" t="inlineStr">
         <is>
           <t>35360</t>
         </is>
       </c>
-      <c r="V593" t="inlineStr">
+      <c r="Y593" t="inlineStr">
         <is>
           <t>35361</t>
         </is>
@@ -35061,7 +35091,7 @@
           <t>HOUNSLOW Richard</t>
         </is>
       </c>
-      <c r="U594" t="inlineStr">
+      <c r="X594" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -35124,12 +35154,12 @@
           <t>BISO Hugo</t>
         </is>
       </c>
-      <c r="U595" t="inlineStr">
+      <c r="X595" t="inlineStr">
         <is>
           <t>35403</t>
         </is>
       </c>
-      <c r="V595" t="inlineStr">
+      <c r="Y595" t="inlineStr">
         <is>
           <t>35229</t>
         </is>
@@ -35192,12 +35222,12 @@
           <t>PECHE Matthieu</t>
         </is>
       </c>
-      <c r="U596" t="inlineStr">
+      <c r="X596" t="inlineStr">
         <is>
           <t>35350</t>
         </is>
       </c>
-      <c r="V596" t="inlineStr">
+      <c r="Y596" t="inlineStr">
         <is>
           <t>35400</t>
         </is>
@@ -35255,7 +35285,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U597" t="inlineStr">
+      <c r="X597" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -35313,7 +35343,7 @@
           <t>BOUZIDI Carole</t>
         </is>
       </c>
-      <c r="U598" t="inlineStr">
+      <c r="X598" t="inlineStr">
         <is>
           <t>35231</t>
         </is>
@@ -35371,7 +35401,7 @@
           <t>HILGERTOVA Stepanka</t>
         </is>
       </c>
-      <c r="U599" t="inlineStr">
+      <c r="X599" t="inlineStr">
         <is>
           <t>35035</t>
         </is>
@@ -35429,7 +35459,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U600" t="inlineStr">
+      <c r="X600" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -35487,7 +35517,7 @@
           <t>LI Tong</t>
         </is>
       </c>
-      <c r="U601" t="inlineStr">
+      <c r="X601" t="inlineStr">
         <is>
           <t>52023</t>
         </is>
@@ -35545,7 +35575,7 @@
           <t>OBLINGER-PETERS Violetta</t>
         </is>
       </c>
-      <c r="U602" t="inlineStr">
+      <c r="X602" t="inlineStr">
         <is>
           <t>35289</t>
         </is>
@@ -35603,7 +35633,7 @@
           <t>GIAI PRON Maria Clara</t>
         </is>
       </c>
-      <c r="U603" t="inlineStr">
+      <c r="X603" t="inlineStr">
         <is>
           <t>35218</t>
         </is>
@@ -35714,7 +35744,7 @@
           <t>GOIKOETXEA Irati</t>
         </is>
       </c>
-      <c r="U605" t="inlineStr">
+      <c r="X605" t="inlineStr">
         <is>
           <t>35761</t>
         </is>
@@ -35825,7 +35855,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U607" t="inlineStr">
+      <c r="X607" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -35883,7 +35913,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U608" t="inlineStr">
+      <c r="X608" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -35941,7 +35971,7 @@
           <t>PEROVA Aleksandra</t>
         </is>
       </c>
-      <c r="U609" t="inlineStr">
+      <c r="X609" t="inlineStr">
         <is>
           <t>35256</t>
         </is>
@@ -35999,7 +36029,7 @@
           <t>YAZAWA Aki</t>
         </is>
       </c>
-      <c r="U610" t="inlineStr">
+      <c r="X610" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
@@ -36057,7 +36087,7 @@
           <t>VOJTOVA Veronika</t>
         </is>
       </c>
-      <c r="U611" t="inlineStr">
+      <c r="X611" t="inlineStr">
         <is>
           <t>35945</t>
         </is>
@@ -36115,7 +36145,7 @@
           <t>LEITNER Lisa</t>
         </is>
       </c>
-      <c r="U612" t="inlineStr">
+      <c r="X612" t="inlineStr">
         <is>
           <t>35305</t>
         </is>
@@ -36173,7 +36203,7 @@
           <t>LI Lu</t>
         </is>
       </c>
-      <c r="U613" t="inlineStr">
+      <c r="X613" t="inlineStr">
         <is>
           <t>37086</t>
         </is>
@@ -36231,7 +36261,7 @@
           <t>KRAGELJ Ursa</t>
         </is>
       </c>
-      <c r="U614" t="inlineStr">
+      <c r="X614" t="inlineStr">
         <is>
           <t>36264</t>
         </is>
@@ -36289,7 +36319,7 @@
           <t>LAFONT Marie-Zelia</t>
         </is>
       </c>
-      <c r="U615" t="inlineStr">
+      <c r="X615" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
@@ -36453,7 +36483,7 @@
           <t>KHARITONOVA Marta</t>
         </is>
       </c>
-      <c r="U618" t="inlineStr">
+      <c r="X618" t="inlineStr">
         <is>
           <t>35257</t>
         </is>
@@ -36564,7 +36594,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U620" t="inlineStr">
+      <c r="X620" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -36622,7 +36652,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U621" t="inlineStr">
+      <c r="X621" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -36680,7 +36710,7 @@
           <t>PENNIE Fiona</t>
         </is>
       </c>
-      <c r="U622" t="inlineStr">
+      <c r="X622" t="inlineStr">
         <is>
           <t>35638</t>
         </is>
@@ -36738,7 +36768,7 @@
           <t>KUDEJOVA Katerina</t>
         </is>
       </c>
-      <c r="U623" t="inlineStr">
+      <c r="X623" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
@@ -36796,7 +36826,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U624" t="inlineStr">
+      <c r="X624" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -36854,7 +36884,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U625" t="inlineStr">
+      <c r="X625" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -36912,7 +36942,7 @@
           <t>FER Emilie</t>
         </is>
       </c>
-      <c r="U626" t="inlineStr">
+      <c r="X626" t="inlineStr">
         <is>
           <t>35314</t>
         </is>
@@ -36985,12 +37015,12 @@
           <t>BECKER Thomas</t>
         </is>
       </c>
-      <c r="U627" t="inlineStr">
+      <c r="X627" t="inlineStr">
         <is>
           <t>35139</t>
         </is>
       </c>
-      <c r="V627" t="inlineStr">
+      <c r="Y627" t="inlineStr">
         <is>
           <t>35143</t>
         </is>
@@ -37063,12 +37093,12 @@
           <t>BISO Hugo</t>
         </is>
       </c>
-      <c r="U628" t="inlineStr">
+      <c r="X628" t="inlineStr">
         <is>
           <t>35403</t>
         </is>
       </c>
-      <c r="V628" t="inlineStr">
+      <c r="Y628" t="inlineStr">
         <is>
           <t>35229</t>
         </is>
@@ -37141,12 +37171,12 @@
           <t>MAJERCZAK Grzegorz</t>
         </is>
       </c>
-      <c r="U629" t="inlineStr">
+      <c r="X629" t="inlineStr">
         <is>
           <t>35085</t>
         </is>
       </c>
-      <c r="V629" t="inlineStr">
+      <c r="Y629" t="inlineStr">
         <is>
           <t>35086</t>
         </is>
@@ -37219,12 +37249,12 @@
           <t>TALJAT Saso</t>
         </is>
       </c>
-      <c r="U630" t="inlineStr">
+      <c r="X630" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
       </c>
-      <c r="V630" t="inlineStr">
+      <c r="Y630" t="inlineStr">
         <is>
           <t>36270</t>
         </is>
@@ -37297,12 +37327,12 @@
           <t>POCHWALA Marcin</t>
         </is>
       </c>
-      <c r="U631" t="inlineStr">
+      <c r="X631" t="inlineStr">
         <is>
           <t>35080</t>
         </is>
       </c>
-      <c r="V631" t="inlineStr">
+      <c r="Y631" t="inlineStr">
         <is>
           <t>35079</t>
         </is>
@@ -37375,12 +37405,12 @@
           <t>PECHE Matthieu</t>
         </is>
       </c>
-      <c r="U632" t="inlineStr">
+      <c r="X632" t="inlineStr">
         <is>
           <t>35350</t>
         </is>
       </c>
-      <c r="V632" t="inlineStr">
+      <c r="Y632" t="inlineStr">
         <is>
           <t>35400</t>
         </is>
@@ -37453,12 +37483,12 @@
           <t>BENZIEN Jan</t>
         </is>
       </c>
-      <c r="U633" t="inlineStr">
+      <c r="X633" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
       </c>
-      <c r="V633" t="inlineStr">
+      <c r="Y633" t="inlineStr">
         <is>
           <t>35134</t>
         </is>
@@ -37599,12 +37629,12 @@
           <t>BRZEZINSKI Andrzej</t>
         </is>
       </c>
-      <c r="U635" t="inlineStr">
+      <c r="X635" t="inlineStr">
         <is>
           <t>35082</t>
         </is>
       </c>
-      <c r="V635" t="inlineStr">
+      <c r="Y635" t="inlineStr">
         <is>
           <t>35081</t>
         </is>
@@ -37677,7 +37707,7 @@
           <t>HOUNSLOW Richard</t>
         </is>
       </c>
-      <c r="U636" t="inlineStr">
+      <c r="X636" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -37745,7 +37775,7 @@
           <t>HILGERTOVA Stepanka</t>
         </is>
       </c>
-      <c r="U637" t="inlineStr">
+      <c r="X637" t="inlineStr">
         <is>
           <t>35035</t>
         </is>
@@ -37876,7 +37906,7 @@
           <t>PENNIE Fiona</t>
         </is>
       </c>
-      <c r="U639" t="inlineStr">
+      <c r="X639" t="inlineStr">
         <is>
           <t>35638</t>
         </is>
@@ -38007,7 +38037,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U641" t="inlineStr">
+      <c r="X641" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -38138,7 +38168,7 @@
           <t>KUDEJOVA Katerina</t>
         </is>
       </c>
-      <c r="U643" t="inlineStr">
+      <c r="X643" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
@@ -38206,7 +38236,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U644" t="inlineStr">
+      <c r="X644" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -38337,7 +38367,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U646" t="inlineStr">
+      <c r="X646" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -38402,17 +38432,62 @@
       </c>
       <c r="R647" t="inlineStr">
         <is>
-          <t>CORREA Charles/OLIVEIRA Anderson</t>
+          <t>CORREA Charles</t>
         </is>
       </c>
       <c r="S647" t="inlineStr">
         <is>
-          <t>CURCEL Leonardo/RODRIGUES Fabio</t>
+          <t>OLIVEIRA Anderson</t>
         </is>
       </c>
       <c r="T647" t="inlineStr">
         <is>
-          <t>AVERSA Pedro/DE SOUZA Rafael</t>
+          <t>CURCEL Leonardo</t>
+        </is>
+      </c>
+      <c r="U647" t="inlineStr">
+        <is>
+          <t>RODRIGUES Fabio</t>
+        </is>
+      </c>
+      <c r="V647" t="inlineStr">
+        <is>
+          <t>AVERSA Pedro</t>
+        </is>
+      </c>
+      <c r="W647" t="inlineStr">
+        <is>
+          <t>DE SOUZA Rafael</t>
+        </is>
+      </c>
+      <c r="X647" t="inlineStr">
+        <is>
+          <t>38018</t>
+        </is>
+      </c>
+      <c r="Y647" t="inlineStr">
+        <is>
+          <t>38020</t>
+        </is>
+      </c>
+      <c r="Z647" t="inlineStr">
+        <is>
+          <t>38014</t>
+        </is>
+      </c>
+      <c r="AA647" t="inlineStr">
+        <is>
+          <t>38023</t>
+        </is>
+      </c>
+      <c r="AB647" t="inlineStr">
+        <is>
+          <t>60498</t>
+        </is>
+      </c>
+      <c r="AC647" t="inlineStr">
+        <is>
+          <t>38021</t>
         </is>
       </c>
     </row>
@@ -38475,17 +38550,52 @@
       </c>
       <c r="R648" t="inlineStr">
         <is>
-          <t>MCEWAN Devin/EICHFELD Casey</t>
+          <t>MCEWAN Devin</t>
         </is>
       </c>
       <c r="S648" t="inlineStr">
         <is>
-          <t>SMITH Tyler/DENNIS Tad</t>
+          <t>EICHFELD Casey</t>
         </is>
       </c>
       <c r="T648" t="inlineStr">
         <is>
-          <t>LONG Chad/LONG Kenneth</t>
+          <t>SMITH Tyler</t>
+        </is>
+      </c>
+      <c r="U648" t="inlineStr">
+        <is>
+          <t>DENNIS Tad</t>
+        </is>
+      </c>
+      <c r="V648" t="inlineStr">
+        <is>
+          <t>LONG Chad</t>
+        </is>
+      </c>
+      <c r="W648" t="inlineStr">
+        <is>
+          <t>LONG Kenneth</t>
+        </is>
+      </c>
+      <c r="X648" t="inlineStr">
+        <is>
+          <t>35068</t>
+        </is>
+      </c>
+      <c r="Y648" t="inlineStr">
+        <is>
+          <t>35067</t>
+        </is>
+      </c>
+      <c r="Z648" t="inlineStr">
+        <is>
+          <t>51904</t>
+        </is>
+      </c>
+      <c r="AA648" t="inlineStr">
+        <is>
+          <t>42253</t>
         </is>
       </c>
     </row>
@@ -38548,17 +38658,42 @@
       </c>
       <c r="R649" t="inlineStr">
         <is>
-          <t>FLORENCE David/HOUNSLOW Richard</t>
+          <t>FLORENCE David</t>
         </is>
       </c>
       <c r="S649" t="inlineStr">
         <is>
-          <t>PROCTOR Mark/STOTT Etienne</t>
+          <t>HOUNSLOW Richard</t>
         </is>
       </c>
       <c r="T649" t="inlineStr">
         <is>
-          <t>BURGESS Adam/PITT Greg</t>
+          <t>PROCTOR Mark</t>
+        </is>
+      </c>
+      <c r="U649" t="inlineStr">
+        <is>
+          <t>STOTT Etienne</t>
+        </is>
+      </c>
+      <c r="V649" t="inlineStr">
+        <is>
+          <t>BURGESS Adam</t>
+        </is>
+      </c>
+      <c r="W649" t="inlineStr">
+        <is>
+          <t>PITT Greg</t>
+        </is>
+      </c>
+      <c r="X649" t="inlineStr">
+        <is>
+          <t>35634</t>
+        </is>
+      </c>
+      <c r="AB649" t="inlineStr">
+        <is>
+          <t>35647</t>
         </is>
       </c>
     </row>
@@ -38621,17 +38756,62 @@
       </c>
       <c r="R650" t="inlineStr">
         <is>
-          <t>SZCZEPANSKI Piotr/POCHWALA Marcin</t>
+          <t>SZCZEPANSKI Piotr</t>
         </is>
       </c>
       <c r="S650" t="inlineStr">
         <is>
-          <t>BRZEZINSKI Filip/BRZEZINSKI Andrzej</t>
+          <t>POCHWALA Marcin</t>
         </is>
       </c>
       <c r="T650" t="inlineStr">
         <is>
-          <t>WIERCIOCH Michal/MAJERCZAK Grzegorz</t>
+          <t>BRZEZINSKI Filip</t>
+        </is>
+      </c>
+      <c r="U650" t="inlineStr">
+        <is>
+          <t>BRZEZINSKI Andrzej</t>
+        </is>
+      </c>
+      <c r="V650" t="inlineStr">
+        <is>
+          <t>WIERCIOCH Michal</t>
+        </is>
+      </c>
+      <c r="W650" t="inlineStr">
+        <is>
+          <t>MAJERCZAK Grzegorz</t>
+        </is>
+      </c>
+      <c r="X650" t="inlineStr">
+        <is>
+          <t>35080</t>
+        </is>
+      </c>
+      <c r="Y650" t="inlineStr">
+        <is>
+          <t>35079</t>
+        </is>
+      </c>
+      <c r="Z650" t="inlineStr">
+        <is>
+          <t>35082</t>
+        </is>
+      </c>
+      <c r="AA650" t="inlineStr">
+        <is>
+          <t>35081</t>
+        </is>
+      </c>
+      <c r="AB650" t="inlineStr">
+        <is>
+          <t>35085</t>
+        </is>
+      </c>
+      <c r="AC650" t="inlineStr">
+        <is>
+          <t>35086</t>
         </is>
       </c>
     </row>
@@ -38694,17 +38874,62 @@
       </c>
       <c r="R651" t="inlineStr">
         <is>
-          <t>KUZNETSOV Mikhail/LARIONOV Dmitry</t>
+          <t>KUZNETSOV Mikhail</t>
         </is>
       </c>
       <c r="S651" t="inlineStr">
         <is>
-          <t>SUSLOV Alexei/OBRAZTSOV Maxim</t>
+          <t>LARIONOV Dmitry</t>
         </is>
       </c>
       <c r="T651" t="inlineStr">
         <is>
-          <t>USHAKOV Anton/USHAKOV Artem</t>
+          <t>SUSLOV Alexei</t>
+        </is>
+      </c>
+      <c r="U651" t="inlineStr">
+        <is>
+          <t>OBRAZTSOV Maxim</t>
+        </is>
+      </c>
+      <c r="V651" t="inlineStr">
+        <is>
+          <t>USHAKOV Anton</t>
+        </is>
+      </c>
+      <c r="W651" t="inlineStr">
+        <is>
+          <t>USHAKOV Artem</t>
+        </is>
+      </c>
+      <c r="X651" t="inlineStr">
+        <is>
+          <t>35449</t>
+        </is>
+      </c>
+      <c r="Y651" t="inlineStr">
+        <is>
+          <t>35450</t>
+        </is>
+      </c>
+      <c r="Z651" t="inlineStr">
+        <is>
+          <t>35770</t>
+        </is>
+      </c>
+      <c r="AA651" t="inlineStr">
+        <is>
+          <t>35767</t>
+        </is>
+      </c>
+      <c r="AB651" t="inlineStr">
+        <is>
+          <t>35454</t>
+        </is>
+      </c>
+      <c r="AC651" t="inlineStr">
+        <is>
+          <t>35455</t>
         </is>
       </c>
     </row>
@@ -38767,17 +38992,62 @@
       </c>
       <c r="R652" t="inlineStr">
         <is>
-          <t>YE Yongtao/HUANG Yongze</t>
+          <t>YE Yongtao</t>
         </is>
       </c>
       <c r="S652" t="inlineStr">
         <is>
-          <t>ZHANG Hang/DENG Xiao</t>
+          <t>HUANG Yongze</t>
         </is>
       </c>
       <c r="T652" t="inlineStr">
         <is>
-          <t>YU Hongmin/CHEN Jin</t>
+          <t>ZHANG Hang</t>
+        </is>
+      </c>
+      <c r="U652" t="inlineStr">
+        <is>
+          <t>DENG Xiao</t>
+        </is>
+      </c>
+      <c r="V652" t="inlineStr">
+        <is>
+          <t>YU Hongmin</t>
+        </is>
+      </c>
+      <c r="W652" t="inlineStr">
+        <is>
+          <t>CHEN Jin</t>
+        </is>
+      </c>
+      <c r="X652" t="inlineStr">
+        <is>
+          <t>52028</t>
+        </is>
+      </c>
+      <c r="Y652" t="inlineStr">
+        <is>
+          <t>52029</t>
+        </is>
+      </c>
+      <c r="Z652" t="inlineStr">
+        <is>
+          <t>42239</t>
+        </is>
+      </c>
+      <c r="AA652" t="inlineStr">
+        <is>
+          <t>42240</t>
+        </is>
+      </c>
+      <c r="AB652" t="inlineStr">
+        <is>
+          <t>42237</t>
+        </is>
+      </c>
+      <c r="AC652" t="inlineStr">
+        <is>
+          <t>42238</t>
         </is>
       </c>
     </row>
@@ -38840,17 +39110,62 @@
       </c>
       <c r="R653" t="inlineStr">
         <is>
-          <t>ANTON Franz/BENZIEN Jan</t>
+          <t>ANTON Franz</t>
         </is>
       </c>
       <c r="S653" t="inlineStr">
         <is>
-          <t>BEHLING Robert/BECKER Thomas</t>
+          <t>BENZIEN Jan</t>
         </is>
       </c>
       <c r="T653" t="inlineStr">
         <is>
-          <t>MUELLER Kai/MUELLER Kevin</t>
+          <t>BEHLING Robert</t>
+        </is>
+      </c>
+      <c r="U653" t="inlineStr">
+        <is>
+          <t>BECKER Thomas</t>
+        </is>
+      </c>
+      <c r="V653" t="inlineStr">
+        <is>
+          <t>MUELLER Kai</t>
+        </is>
+      </c>
+      <c r="W653" t="inlineStr">
+        <is>
+          <t>MUELLER Kevin</t>
+        </is>
+      </c>
+      <c r="X653" t="inlineStr">
+        <is>
+          <t>35137</t>
+        </is>
+      </c>
+      <c r="Y653" t="inlineStr">
+        <is>
+          <t>35134</t>
+        </is>
+      </c>
+      <c r="Z653" t="inlineStr">
+        <is>
+          <t>35139</t>
+        </is>
+      </c>
+      <c r="AA653" t="inlineStr">
+        <is>
+          <t>35143</t>
+        </is>
+      </c>
+      <c r="AB653" t="inlineStr">
+        <is>
+          <t>35148</t>
+        </is>
+      </c>
+      <c r="AC653" t="inlineStr">
+        <is>
+          <t>35149</t>
         </is>
       </c>
     </row>
@@ -38913,17 +39228,62 @@
       </c>
       <c r="R654" t="inlineStr">
         <is>
-          <t>KARLOVSKY Ondrej/JANE Jakub</t>
+          <t>KARLOVSKY Ondrej</t>
         </is>
       </c>
       <c r="S654" t="inlineStr">
         <is>
-          <t>KASPAR Jonas/SINDLER Marek</t>
+          <t>JANE Jakub</t>
         </is>
       </c>
       <c r="T654" t="inlineStr">
         <is>
-          <t>KOPLIK Tomas/VRZAN Jakub</t>
+          <t>KASPAR Jonas</t>
+        </is>
+      </c>
+      <c r="U654" t="inlineStr">
+        <is>
+          <t>SINDLER Marek</t>
+        </is>
+      </c>
+      <c r="V654" t="inlineStr">
+        <is>
+          <t>KOPLIK Tomas</t>
+        </is>
+      </c>
+      <c r="W654" t="inlineStr">
+        <is>
+          <t>VRZAN Jakub</t>
+        </is>
+      </c>
+      <c r="X654" t="inlineStr">
+        <is>
+          <t>35060</t>
+        </is>
+      </c>
+      <c r="Y654" t="inlineStr">
+        <is>
+          <t>35061</t>
+        </is>
+      </c>
+      <c r="Z654" t="inlineStr">
+        <is>
+          <t>35062</t>
+        </is>
+      </c>
+      <c r="AA654" t="inlineStr">
+        <is>
+          <t>35063</t>
+        </is>
+      </c>
+      <c r="AB654" t="inlineStr">
+        <is>
+          <t>35042</t>
+        </is>
+      </c>
+      <c r="AC654" t="inlineStr">
+        <is>
+          <t>35043</t>
         </is>
       </c>
     </row>
@@ -38986,17 +39346,62 @@
       </c>
       <c r="R655" t="inlineStr">
         <is>
-          <t>HOCHSCHORNER Pavol/HOCHSCHORNER Peter</t>
+          <t>HOCHSCHORNER Pavol</t>
         </is>
       </c>
       <c r="S655" t="inlineStr">
         <is>
-          <t>SKANTAR Ladislav/SKANTAR Peter</t>
+          <t>HOCHSCHORNER Peter</t>
         </is>
       </c>
       <c r="T655" t="inlineStr">
         <is>
-          <t>KUCERA Tomas/BATIK Jan</t>
+          <t>SKANTAR Ladislav</t>
+        </is>
+      </c>
+      <c r="U655" t="inlineStr">
+        <is>
+          <t>SKANTAR Peter</t>
+        </is>
+      </c>
+      <c r="V655" t="inlineStr">
+        <is>
+          <t>KUCERA Tomas</t>
+        </is>
+      </c>
+      <c r="W655" t="inlineStr">
+        <is>
+          <t>BATIK Jan</t>
+        </is>
+      </c>
+      <c r="X655" t="inlineStr">
+        <is>
+          <t>35356</t>
+        </is>
+      </c>
+      <c r="Y655" t="inlineStr">
+        <is>
+          <t>35357</t>
+        </is>
+      </c>
+      <c r="Z655" t="inlineStr">
+        <is>
+          <t>35360</t>
+        </is>
+      </c>
+      <c r="AA655" t="inlineStr">
+        <is>
+          <t>35361</t>
+        </is>
+      </c>
+      <c r="AB655" t="inlineStr">
+        <is>
+          <t>35368</t>
+        </is>
+      </c>
+      <c r="AC655" t="inlineStr">
+        <is>
+          <t>35367</t>
         </is>
       </c>
     </row>
@@ -39059,17 +39464,62 @@
       </c>
       <c r="R656" t="inlineStr">
         <is>
-          <t>PICCO Pierre/BISO Hugo</t>
+          <t>PICCO Pierre</t>
         </is>
       </c>
       <c r="S656" t="inlineStr">
         <is>
-          <t>KLAUSS Gauthier/PECHE Matthieu</t>
+          <t>BISO Hugo</t>
         </is>
       </c>
       <c r="T656" t="inlineStr">
         <is>
-          <t>PRIGENT Yves/KERVELLA Loic</t>
+          <t>KLAUSS Gauthier</t>
+        </is>
+      </c>
+      <c r="U656" t="inlineStr">
+        <is>
+          <t>PECHE Matthieu</t>
+        </is>
+      </c>
+      <c r="V656" t="inlineStr">
+        <is>
+          <t>PRIGENT Yves</t>
+        </is>
+      </c>
+      <c r="W656" t="inlineStr">
+        <is>
+          <t>KERVELLA Loic</t>
+        </is>
+      </c>
+      <c r="X656" t="inlineStr">
+        <is>
+          <t>35403</t>
+        </is>
+      </c>
+      <c r="Y656" t="inlineStr">
+        <is>
+          <t>35229</t>
+        </is>
+      </c>
+      <c r="Z656" t="inlineStr">
+        <is>
+          <t>35350</t>
+        </is>
+      </c>
+      <c r="AA656" t="inlineStr">
+        <is>
+          <t>35400</t>
+        </is>
+      </c>
+      <c r="AB656" t="inlineStr">
+        <is>
+          <t>35671</t>
+        </is>
+      </c>
+      <c r="AC656" t="inlineStr">
+        <is>
+          <t>35672</t>
         </is>
       </c>
     </row>
@@ -39145,17 +39595,17 @@
           <t>XU Yanru</t>
         </is>
       </c>
-      <c r="U657" t="inlineStr">
+      <c r="X657" t="inlineStr">
         <is>
           <t>37086</t>
         </is>
       </c>
-      <c r="V657" t="inlineStr">
+      <c r="Y657" t="inlineStr">
         <is>
           <t>52023</t>
         </is>
       </c>
-      <c r="W657" t="inlineStr">
+      <c r="Z657" t="inlineStr">
         <is>
           <t>63801</t>
         </is>
@@ -39233,12 +39683,12 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U658" t="inlineStr">
+      <c r="X658" t="inlineStr">
         <is>
           <t>35331</t>
         </is>
       </c>
-      <c r="W658" t="inlineStr">
+      <c r="Z658" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -39316,17 +39766,17 @@
           <t>ITO Yoshika</t>
         </is>
       </c>
-      <c r="U659" t="inlineStr">
+      <c r="X659" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
       </c>
-      <c r="V659" t="inlineStr">
+      <c r="Y659" t="inlineStr">
         <is>
           <t>36487</t>
         </is>
       </c>
-      <c r="W659" t="inlineStr">
+      <c r="Z659" t="inlineStr">
         <is>
           <t>36647</t>
         </is>
@@ -39404,17 +39854,17 @@
           <t>MARTINEZ Marta</t>
         </is>
       </c>
-      <c r="U660" t="inlineStr">
+      <c r="X660" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
       </c>
-      <c r="V660" t="inlineStr">
+      <c r="Y660" t="inlineStr">
         <is>
           <t>35761</t>
         </is>
       </c>
-      <c r="W660" t="inlineStr">
+      <c r="Z660" t="inlineStr">
         <is>
           <t>35760</t>
         </is>
@@ -39492,12 +39942,12 @@
           <t>BORROWS Alison</t>
         </is>
       </c>
-      <c r="V661" t="inlineStr">
+      <c r="Y661" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
       </c>
-      <c r="W661" t="inlineStr">
+      <c r="Z661" t="inlineStr">
         <is>
           <t>38440</t>
         </is>
@@ -39575,17 +40025,17 @@
           <t>IFARRAGUERRI Anna Maria</t>
         </is>
       </c>
-      <c r="U662" t="inlineStr">
+      <c r="X662" t="inlineStr">
         <is>
           <t>36363</t>
         </is>
       </c>
-      <c r="V662" t="inlineStr">
+      <c r="Y662" t="inlineStr">
         <is>
           <t>35369</t>
         </is>
       </c>
-      <c r="W662" t="inlineStr">
+      <c r="Z662" t="inlineStr">
         <is>
           <t>39209</t>
         </is>
@@ -39663,17 +40113,17 @@
           <t>DENHOLLANDER Jazmyne</t>
         </is>
       </c>
-      <c r="U663" t="inlineStr">
+      <c r="X663" t="inlineStr">
         <is>
           <t>35542</t>
         </is>
       </c>
-      <c r="V663" t="inlineStr">
+      <c r="Y663" t="inlineStr">
         <is>
           <t>35533</t>
         </is>
       </c>
-      <c r="W663" t="inlineStr">
+      <c r="Z663" t="inlineStr">
         <is>
           <t>37165</t>
         </is>
@@ -39751,7 +40201,7 @@
           <t>NEAVE Elizabeth</t>
         </is>
       </c>
-      <c r="U664" t="inlineStr">
+      <c r="X664" t="inlineStr">
         <is>
           <t>35638</t>
         </is>
@@ -39829,17 +40279,17 @@
           <t>KHARITONOVA Marta</t>
         </is>
       </c>
-      <c r="U665" t="inlineStr">
+      <c r="X665" t="inlineStr">
         <is>
           <t>35131</t>
         </is>
       </c>
-      <c r="V665" t="inlineStr">
+      <c r="Y665" t="inlineStr">
         <is>
           <t>35256</t>
         </is>
       </c>
-      <c r="W665" t="inlineStr">
+      <c r="Z665" t="inlineStr">
         <is>
           <t>35257</t>
         </is>
@@ -39917,17 +40367,17 @@
           <t>HILGERTOVA Stepanka</t>
         </is>
       </c>
-      <c r="U666" t="inlineStr">
+      <c r="X666" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
       </c>
-      <c r="V666" t="inlineStr">
+      <c r="Y666" t="inlineStr">
         <is>
           <t>35945</t>
         </is>
       </c>
-      <c r="W666" t="inlineStr">
+      <c r="Z666" t="inlineStr">
         <is>
           <t>35035</t>
         </is>
@@ -40005,12 +40455,12 @@
           <t>FRITSCHE Lisa</t>
         </is>
       </c>
-      <c r="V667" t="inlineStr">
+      <c r="Y667" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
       </c>
-      <c r="W667" t="inlineStr">
+      <c r="Z667" t="inlineStr">
         <is>
           <t>39883</t>
         </is>
@@ -40088,17 +40538,17 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U668" t="inlineStr">
+      <c r="X668" t="inlineStr">
         <is>
           <t>36264</t>
         </is>
       </c>
-      <c r="V668" t="inlineStr">
+      <c r="Y668" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
       </c>
-      <c r="W668" t="inlineStr">
+      <c r="Z668" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -40176,17 +40626,17 @@
           <t>NEVARILOVA Kristina</t>
         </is>
       </c>
-      <c r="U669" t="inlineStr">
+      <c r="X669" t="inlineStr">
         <is>
           <t>35366</t>
         </is>
       </c>
-      <c r="V669" t="inlineStr">
+      <c r="Y669" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
       </c>
-      <c r="W669" t="inlineStr">
+      <c r="Z669" t="inlineStr">
         <is>
           <t>35467</t>
         </is>
@@ -40264,17 +40714,17 @@
           <t>LEITNER Lisa</t>
         </is>
       </c>
-      <c r="U670" t="inlineStr">
+      <c r="X670" t="inlineStr">
         <is>
           <t>35289</t>
         </is>
       </c>
-      <c r="V670" t="inlineStr">
+      <c r="Y670" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
       </c>
-      <c r="W670" t="inlineStr">
+      <c r="Z670" t="inlineStr">
         <is>
           <t>35305</t>
         </is>
@@ -40352,17 +40802,17 @@
           <t>FER Emilie</t>
         </is>
       </c>
-      <c r="U671" t="inlineStr">
+      <c r="X671" t="inlineStr">
         <is>
           <t>35231</t>
         </is>
       </c>
-      <c r="V671" t="inlineStr">
+      <c r="Y671" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
       </c>
-      <c r="W671" t="inlineStr">
+      <c r="Z671" t="inlineStr">
         <is>
           <t>35314</t>
         </is>
@@ -40708,7 +41158,7 @@
           <t>RAK Tomas</t>
         </is>
       </c>
-      <c r="U678" t="inlineStr">
+      <c r="X678" t="inlineStr">
         <is>
           <t>35056</t>
         </is>
@@ -40766,7 +41216,7 @@
           <t>JEGOU Liam</t>
         </is>
       </c>
-      <c r="U679" t="inlineStr">
+      <c r="X679" t="inlineStr">
         <is>
           <t>35820</t>
         </is>
@@ -40824,7 +41274,7 @@
           <t>JANE Michal</t>
         </is>
       </c>
-      <c r="U680" t="inlineStr">
+      <c r="X680" t="inlineStr">
         <is>
           <t>35059</t>
         </is>
@@ -40882,7 +41332,7 @@
           <t>CIPRESSI Stefano</t>
         </is>
       </c>
-      <c r="U681" t="inlineStr">
+      <c r="X681" t="inlineStr">
         <is>
           <t>35495</t>
         </is>
@@ -40940,7 +41390,7 @@
           <t>DOMENJO Jordi</t>
         </is>
       </c>
-      <c r="U682" t="inlineStr">
+      <c r="X682" t="inlineStr">
         <is>
           <t>35739</t>
         </is>
@@ -40998,7 +41448,7 @@
           <t>COLAZINGARI Roberto</t>
         </is>
       </c>
-      <c r="U683" t="inlineStr">
+      <c r="X683" t="inlineStr">
         <is>
           <t>35223</t>
         </is>
@@ -41109,7 +41559,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U685" t="inlineStr">
+      <c r="X685" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -41167,7 +41617,7 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U686" t="inlineStr">
+      <c r="X686" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -41225,7 +41675,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U687" t="inlineStr">
+      <c r="X687" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -41283,7 +41733,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U688" t="inlineStr">
+      <c r="X688" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -41341,7 +41791,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U689" t="inlineStr">
+      <c r="X689" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -41399,7 +41849,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U690" t="inlineStr">
+      <c r="X690" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -41457,7 +41907,7 @@
           <t>SMEDLEY Cameron</t>
         </is>
       </c>
-      <c r="U691" t="inlineStr">
+      <c r="X691" t="inlineStr">
         <is>
           <t>35543</t>
         </is>
@@ -41515,7 +41965,7 @@
           <t>FLORENCE David</t>
         </is>
       </c>
-      <c r="U692" t="inlineStr">
+      <c r="X692" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -41573,7 +42023,7 @@
           <t>ELOSEGI Ander</t>
         </is>
       </c>
-      <c r="U693" t="inlineStr">
+      <c r="X693" t="inlineStr">
         <is>
           <t>35785</t>
         </is>
@@ -41631,7 +42081,7 @@
           <t>SETKIN Kirill</t>
         </is>
       </c>
-      <c r="U694" t="inlineStr">
+      <c r="X694" t="inlineStr">
         <is>
           <t>35457</t>
         </is>
@@ -41689,7 +42139,7 @@
           <t>LIPATOV Aleksandr</t>
         </is>
       </c>
-      <c r="U695" t="inlineStr">
+      <c r="X695" t="inlineStr">
         <is>
           <t>35451</t>
         </is>
@@ -41747,7 +42197,7 @@
           <t>TILLARD Pierre-Antoine</t>
         </is>
       </c>
-      <c r="U696" t="inlineStr">
+      <c r="X696" t="inlineStr">
         <is>
           <t>35413</t>
         </is>
@@ -41805,7 +42255,7 @@
           <t>PESCHIER Nicolas</t>
         </is>
       </c>
-      <c r="U697" t="inlineStr">
+      <c r="X697" t="inlineStr">
         <is>
           <t>35401</t>
         </is>
@@ -41863,7 +42313,7 @@
           <t>JEZEK Stanislav</t>
         </is>
       </c>
-      <c r="U698" t="inlineStr">
+      <c r="X698" t="inlineStr">
         <is>
           <t>35037</t>
         </is>
@@ -41921,7 +42371,7 @@
           <t>JEFFERY Robin</t>
         </is>
       </c>
-      <c r="U699" t="inlineStr">
+      <c r="X699" t="inlineStr">
         <is>
           <t>36525</t>
         </is>
@@ -41979,7 +42429,7 @@
           <t>HANEDA Takuya</t>
         </is>
       </c>
-      <c r="U700" t="inlineStr">
+      <c r="X700" t="inlineStr">
         <is>
           <t>36481</t>
         </is>
@@ -42037,7 +42487,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U701" t="inlineStr">
+      <c r="X701" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -42095,7 +42545,7 @@
           <t>THOMAS Martin</t>
         </is>
       </c>
-      <c r="U702" t="inlineStr">
+      <c r="X702" t="inlineStr">
         <is>
           <t>35412</t>
         </is>
@@ -42153,7 +42603,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U703" t="inlineStr">
+      <c r="X703" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -42211,7 +42661,7 @@
           <t>TASIADIS Sideris</t>
         </is>
       </c>
-      <c r="U704" t="inlineStr">
+      <c r="X704" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
@@ -42269,7 +42719,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U705" t="inlineStr">
+      <c r="X705" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -42327,7 +42777,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U706" t="inlineStr">
+      <c r="X706" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -42385,7 +42835,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U707" t="inlineStr">
+      <c r="X707" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -42443,7 +42893,7 @@
           <t>BIZJAK Nina</t>
         </is>
       </c>
-      <c r="U708" t="inlineStr">
+      <c r="X708" t="inlineStr">
         <is>
           <t>39984</t>
         </is>
@@ -42501,7 +42951,7 @@
           <t>SABITOVA Zulfia</t>
         </is>
       </c>
-      <c r="U709" t="inlineStr">
+      <c r="X709" t="inlineStr">
         <is>
           <t>40572</t>
         </is>
@@ -42559,7 +43009,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U710" t="inlineStr">
+      <c r="X710" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -42617,7 +43067,7 @@
           <t>KUBBE Kira</t>
         </is>
       </c>
-      <c r="U711" t="inlineStr">
+      <c r="X711" t="inlineStr">
         <is>
           <t>43464</t>
         </is>
@@ -42675,7 +43125,7 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U712" t="inlineStr">
+      <c r="X712" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -42786,7 +43236,7 @@
           <t>TIXIER Cecile</t>
         </is>
       </c>
-      <c r="U714" t="inlineStr">
+      <c r="X714" t="inlineStr">
         <is>
           <t>35687</t>
         </is>
@@ -42844,7 +43294,7 @@
           <t>BORROWS Alison</t>
         </is>
       </c>
-      <c r="U715" t="inlineStr">
+      <c r="X715" t="inlineStr">
         <is>
           <t>38440</t>
         </is>
@@ -42955,7 +43405,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U717" t="inlineStr">
+      <c r="X717" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -43013,7 +43463,7 @@
           <t>JACQUET Claire</t>
         </is>
       </c>
-      <c r="U718" t="inlineStr">
+      <c r="X718" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
@@ -43071,7 +43521,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U719" t="inlineStr">
+      <c r="X719" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -43129,7 +43579,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U720" t="inlineStr">
+      <c r="X720" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -43187,7 +43637,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U721" t="inlineStr">
+      <c r="X721" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -43245,7 +43695,7 @@
           <t>SCHMID Julia</t>
         </is>
       </c>
-      <c r="U722" t="inlineStr">
+      <c r="X722" t="inlineStr">
         <is>
           <t>35309</t>
         </is>
@@ -43303,7 +43753,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U723" t="inlineStr">
+      <c r="X723" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -43361,7 +43811,7 @@
           <t>GIBSON Eilidh</t>
         </is>
       </c>
-      <c r="U724" t="inlineStr">
+      <c r="X724" t="inlineStr">
         <is>
           <t>36708</t>
         </is>
@@ -43578,7 +44028,7 @@
           <t>LEITNER Mario</t>
         </is>
       </c>
-      <c r="U728" t="inlineStr">
+      <c r="X728" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
@@ -43636,7 +44086,7 @@
           <t>YAZAWA Kazuki</t>
         </is>
       </c>
-      <c r="U729" t="inlineStr">
+      <c r="X729" t="inlineStr">
         <is>
           <t>36482</t>
         </is>
@@ -43694,7 +44144,7 @@
           <t>HOLMER Erik</t>
         </is>
       </c>
-      <c r="U730" t="inlineStr">
+      <c r="X730" t="inlineStr">
         <is>
           <t>35104</t>
         </is>
@@ -43752,7 +44202,7 @@
           <t>SCHUBERT Sebastian</t>
         </is>
       </c>
-      <c r="U731" t="inlineStr">
+      <c r="X731" t="inlineStr">
         <is>
           <t>35114</t>
         </is>
@@ -43810,7 +44260,7 @@
           <t>DE GENNARO Giovanni</t>
         </is>
       </c>
-      <c r="U732" t="inlineStr">
+      <c r="X732" t="inlineStr">
         <is>
           <t>35244</t>
         </is>
@@ -43868,7 +44318,7 @@
           <t>WERRO Lukas</t>
         </is>
       </c>
-      <c r="U733" t="inlineStr">
+      <c r="X733" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
@@ -43926,7 +44376,7 @@
           <t>NEVEU Boris</t>
         </is>
       </c>
-      <c r="U734" t="inlineStr">
+      <c r="X734" t="inlineStr">
         <is>
           <t>35396</t>
         </is>
@@ -43984,7 +44434,7 @@
           <t>MALEK Andrej</t>
         </is>
       </c>
-      <c r="U735" t="inlineStr">
+      <c r="X735" t="inlineStr">
         <is>
           <t>39246</t>
         </is>
@@ -44042,7 +44492,7 @@
           <t>TSVIET Igor</t>
         </is>
       </c>
-      <c r="U736" t="inlineStr">
+      <c r="X736" t="inlineStr">
         <is>
           <t>35527</t>
         </is>
@@ -44100,7 +44550,7 @@
           <t>OKREGLAK Maciej</t>
         </is>
       </c>
-      <c r="U737" t="inlineStr">
+      <c r="X737" t="inlineStr">
         <is>
           <t>35088</t>
         </is>
@@ -44158,7 +44608,7 @@
           <t>HALCIN Martin</t>
         </is>
       </c>
-      <c r="U738" t="inlineStr">
+      <c r="X738" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
@@ -44216,7 +44666,7 @@
           <t>COMBOT Sebastien</t>
         </is>
       </c>
-      <c r="U739" t="inlineStr">
+      <c r="X739" t="inlineStr">
         <is>
           <t>35234</t>
         </is>
@@ -44327,7 +44777,7 @@
           <t>TAN Ya</t>
         </is>
       </c>
-      <c r="U741" t="inlineStr">
+      <c r="X741" t="inlineStr">
         <is>
           <t>52024</t>
         </is>
@@ -44385,7 +44835,7 @@
           <t>ADACHI Kazuya</t>
         </is>
       </c>
-      <c r="U742" t="inlineStr">
+      <c r="X742" t="inlineStr">
         <is>
           <t>36646</t>
         </is>
@@ -44443,7 +44893,7 @@
           <t>EIGEL Pavel</t>
         </is>
       </c>
-      <c r="U743" t="inlineStr">
+      <c r="X743" t="inlineStr">
         <is>
           <t>35458</t>
         </is>
@@ -44501,7 +44951,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U744" t="inlineStr">
+      <c r="X744" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -44559,7 +45009,7 @@
           <t>BIAZIZZO Mathieu</t>
         </is>
       </c>
-      <c r="U745" t="inlineStr">
+      <c r="X745" t="inlineStr">
         <is>
           <t>35484</t>
         </is>
@@ -44617,7 +45067,7 @@
           <t>ROMEO Andrea</t>
         </is>
       </c>
-      <c r="U746" t="inlineStr">
+      <c r="X746" t="inlineStr">
         <is>
           <t>35502</t>
         </is>
@@ -44675,7 +45125,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U747" t="inlineStr">
+      <c r="X747" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -44733,7 +45183,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U748" t="inlineStr">
+      <c r="X748" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -44791,7 +45241,7 @@
           <t>PETERLIN Janos</t>
         </is>
       </c>
-      <c r="U749" t="inlineStr">
+      <c r="X749" t="inlineStr">
         <is>
           <t>36268</t>
         </is>
@@ -44849,7 +45299,7 @@
           <t>MOLMENTI Daniele</t>
         </is>
       </c>
-      <c r="U750" t="inlineStr">
+      <c r="X750" t="inlineStr">
         <is>
           <t>42017</t>
         </is>
@@ -44907,7 +45357,7 @@
           <t>FORBES-CRYANS Bradley</t>
         </is>
       </c>
-      <c r="U751" t="inlineStr">
+      <c r="X751" t="inlineStr">
         <is>
           <t>36513</t>
         </is>
@@ -44965,7 +45415,7 @@
           <t>GRIMM Alexander</t>
         </is>
       </c>
-      <c r="U752" t="inlineStr">
+      <c r="X752" t="inlineStr">
         <is>
           <t>35112</t>
         </is>
@@ -45023,7 +45473,7 @@
           <t>HRADILEK Vavrinec</t>
         </is>
       </c>
-      <c r="U753" t="inlineStr">
+      <c r="X753" t="inlineStr">
         <is>
           <t>35031</t>
         </is>
@@ -45081,7 +45531,7 @@
           <t>BERSINGER Thomas</t>
         </is>
       </c>
-      <c r="U754" t="inlineStr">
+      <c r="X754" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
@@ -45139,7 +45589,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U755" t="inlineStr">
+      <c r="X755" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -45197,7 +45647,7 @@
           <t>POLACZYK Mateusz</t>
         </is>
       </c>
-      <c r="U756" t="inlineStr">
+      <c r="X756" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
@@ -45255,7 +45705,7 @@
           <t>CRESPO Joan</t>
         </is>
       </c>
-      <c r="U757" t="inlineStr">
+      <c r="X757" t="inlineStr">
         <is>
           <t>35749</t>
         </is>
@@ -45313,7 +45763,7 @@
           <t>MEGLIC Jure</t>
         </is>
       </c>
-      <c r="U758" t="inlineStr">
+      <c r="X758" t="inlineStr">
         <is>
           <t>35590</t>
         </is>
@@ -45371,7 +45821,7 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U759" t="inlineStr">
+      <c r="X759" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -45429,7 +45879,7 @@
           <t>POWELL Richard</t>
         </is>
       </c>
-      <c r="U760" t="inlineStr">
+      <c r="X760" t="inlineStr">
         <is>
           <t>36444</t>
         </is>
@@ -45487,7 +45937,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U761" t="inlineStr">
+      <c r="X761" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -45545,7 +45995,7 @@
           <t>AIGNER Hannes</t>
         </is>
       </c>
-      <c r="U762" t="inlineStr">
+      <c r="X762" t="inlineStr">
         <is>
           <t>35115</t>
         </is>
@@ -45656,7 +46106,7 @@
           <t>BRUS Simon</t>
         </is>
       </c>
-      <c r="U764" t="inlineStr">
+      <c r="X764" t="inlineStr">
         <is>
           <t>39076</t>
         </is>
@@ -45714,7 +46164,7 @@
           <t>KURT Michael</t>
         </is>
       </c>
-      <c r="U765" t="inlineStr">
+      <c r="X765" t="inlineStr">
         <is>
           <t>35346</t>
         </is>
@@ -45772,7 +46222,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U766" t="inlineStr">
+      <c r="X766" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -45830,7 +46280,7 @@
           <t>CLARKE Joseph</t>
         </is>
       </c>
-      <c r="U767" t="inlineStr">
+      <c r="X767" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
@@ -45951,7 +46401,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U769" t="inlineStr">
+      <c r="X769" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -46019,7 +46469,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U770" t="inlineStr">
+      <c r="X770" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -46087,7 +46537,7 @@
           <t>THOMAS Martin</t>
         </is>
       </c>
-      <c r="U771" t="inlineStr">
+      <c r="X771" t="inlineStr">
         <is>
           <t>35412</t>
         </is>
@@ -46155,7 +46605,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U772" t="inlineStr">
+      <c r="X772" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -46223,7 +46673,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U773" t="inlineStr">
+      <c r="X773" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -46291,7 +46741,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U774" t="inlineStr">
+      <c r="X774" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -46359,7 +46809,7 @@
           <t>FLORENCE David</t>
         </is>
       </c>
-      <c r="U775" t="inlineStr">
+      <c r="X775" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -46427,7 +46877,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U776" t="inlineStr">
+      <c r="X776" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -46495,7 +46945,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U777" t="inlineStr">
+      <c r="X777" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -46563,7 +47013,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U778" t="inlineStr">
+      <c r="X778" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -46631,7 +47081,7 @@
           <t>KUBBE Kira</t>
         </is>
       </c>
-      <c r="U779" t="inlineStr">
+      <c r="X779" t="inlineStr">
         <is>
           <t>43464</t>
         </is>
@@ -46699,7 +47149,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U780" t="inlineStr">
+      <c r="X780" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -46767,7 +47217,7 @@
           <t>GIBSON Eilidh</t>
         </is>
       </c>
-      <c r="U781" t="inlineStr">
+      <c r="X781" t="inlineStr">
         <is>
           <t>36708</t>
         </is>
@@ -46835,7 +47285,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U782" t="inlineStr">
+      <c r="X782" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -46903,7 +47353,7 @@
           <t>BORROWS Alison</t>
         </is>
       </c>
-      <c r="U783" t="inlineStr">
+      <c r="X783" t="inlineStr">
         <is>
           <t>38440</t>
         </is>
@@ -47160,7 +47610,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U787" t="inlineStr">
+      <c r="X787" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -47291,7 +47741,7 @@
           <t>COMBOT Sebastien</t>
         </is>
       </c>
-      <c r="U789" t="inlineStr">
+      <c r="X789" t="inlineStr">
         <is>
           <t>35234</t>
         </is>
@@ -47359,7 +47809,7 @@
           <t>OKREGLAK Maciej</t>
         </is>
       </c>
-      <c r="U790" t="inlineStr">
+      <c r="X790" t="inlineStr">
         <is>
           <t>35088</t>
         </is>
@@ -47427,7 +47877,7 @@
           <t>POLACZYK Mateusz</t>
         </is>
       </c>
-      <c r="U791" t="inlineStr">
+      <c r="X791" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
@@ -47495,7 +47945,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U792" t="inlineStr">
+      <c r="X792" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -47563,7 +48013,7 @@
           <t>MOLMENTI Daniele</t>
         </is>
       </c>
-      <c r="U793" t="inlineStr">
+      <c r="X793" t="inlineStr">
         <is>
           <t>42017</t>
         </is>
@@ -47631,7 +48081,7 @@
           <t>ROMEO Andrea</t>
         </is>
       </c>
-      <c r="U794" t="inlineStr">
+      <c r="X794" t="inlineStr">
         <is>
           <t>35502</t>
         </is>
@@ -47699,7 +48149,7 @@
           <t>GRIMM Alexander</t>
         </is>
       </c>
-      <c r="U795" t="inlineStr">
+      <c r="X795" t="inlineStr">
         <is>
           <t>35112</t>
         </is>
@@ -47767,7 +48217,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U796" t="inlineStr">
+      <c r="X796" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -47835,7 +48285,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U797" t="inlineStr">
+      <c r="X797" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -47903,7 +48353,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U798" t="inlineStr">
+      <c r="X798" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -47981,17 +48431,17 @@
           <t>LI Gongte</t>
         </is>
       </c>
-      <c r="U799" t="inlineStr">
+      <c r="X799" t="inlineStr">
         <is>
           <t>60989</t>
         </is>
       </c>
-      <c r="V799" t="inlineStr">
+      <c r="Y799" t="inlineStr">
         <is>
           <t>42638</t>
         </is>
       </c>
-      <c r="W799" t="inlineStr">
+      <c r="Z799" t="inlineStr">
         <is>
           <t>51820</t>
         </is>
@@ -48069,17 +48519,17 @@
           <t>CECCON Paolo</t>
         </is>
       </c>
-      <c r="U800" t="inlineStr">
+      <c r="X800" t="inlineStr">
         <is>
           <t>35495</t>
         </is>
       </c>
-      <c r="V800" t="inlineStr">
+      <c r="Y800" t="inlineStr">
         <is>
           <t>35223</t>
         </is>
       </c>
-      <c r="W800" t="inlineStr">
+      <c r="Z800" t="inlineStr">
         <is>
           <t>39903</t>
         </is>
@@ -48157,17 +48607,17 @@
           <t>SZTUBA Igor</t>
         </is>
       </c>
-      <c r="U801" t="inlineStr">
+      <c r="X801" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
       </c>
-      <c r="V801" t="inlineStr">
+      <c r="Y801" t="inlineStr">
         <is>
           <t>35472</t>
         </is>
       </c>
-      <c r="W801" t="inlineStr">
+      <c r="Z801" t="inlineStr">
         <is>
           <t>35087</t>
         </is>
@@ -48245,17 +48695,17 @@
           <t>HIGGINS Shaun</t>
         </is>
       </c>
-      <c r="U802" t="inlineStr">
+      <c r="X802" t="inlineStr">
         <is>
           <t>36711</t>
         </is>
       </c>
-      <c r="V802" t="inlineStr">
+      <c r="Y802" t="inlineStr">
         <is>
           <t>51862</t>
         </is>
       </c>
-      <c r="W802" t="inlineStr">
+      <c r="Z802" t="inlineStr">
         <is>
           <t>36655</t>
         </is>
@@ -48333,12 +48783,12 @@
           <t>SASAKI Tsubasa</t>
         </is>
       </c>
-      <c r="U803" t="inlineStr">
+      <c r="X803" t="inlineStr">
         <is>
           <t>36481</t>
         </is>
       </c>
-      <c r="V803" t="inlineStr">
+      <c r="Y803" t="inlineStr">
         <is>
           <t>41610</t>
         </is>
@@ -48416,17 +48866,17 @@
           <t>HODSON Ethan</t>
         </is>
       </c>
-      <c r="U804" t="inlineStr">
+      <c r="X804" t="inlineStr">
         <is>
           <t>36524</t>
         </is>
       </c>
-      <c r="V804" t="inlineStr">
+      <c r="Y804" t="inlineStr">
         <is>
           <t>36525</t>
         </is>
       </c>
-      <c r="W804" t="inlineStr">
+      <c r="Z804" t="inlineStr">
         <is>
           <t>38437</t>
         </is>
@@ -48504,12 +48954,12 @@
           <t>SERRA Thiago</t>
         </is>
       </c>
-      <c r="U805" t="inlineStr">
+      <c r="X805" t="inlineStr">
         <is>
           <t>38014</t>
         </is>
       </c>
-      <c r="W805" t="inlineStr">
+      <c r="Z805" t="inlineStr">
         <is>
           <t>41647</t>
         </is>
@@ -48587,17 +49037,17 @@
           <t>OVCHINNIKOV Aleksandr</t>
         </is>
       </c>
-      <c r="U806" t="inlineStr">
+      <c r="X806" t="inlineStr">
         <is>
           <t>35451</t>
         </is>
       </c>
-      <c r="V806" t="inlineStr">
+      <c r="Y806" t="inlineStr">
         <is>
           <t>35457</t>
         </is>
       </c>
-      <c r="W806" t="inlineStr">
+      <c r="Z806" t="inlineStr">
         <is>
           <t>39134</t>
         </is>
@@ -48675,17 +49125,17 @@
           <t>ERGUIN Jon</t>
         </is>
       </c>
-      <c r="U807" t="inlineStr">
+      <c r="X807" t="inlineStr">
         <is>
           <t>35785</t>
         </is>
       </c>
-      <c r="V807" t="inlineStr">
+      <c r="Y807" t="inlineStr">
         <is>
           <t>35739</t>
         </is>
       </c>
-      <c r="W807" t="inlineStr">
+      <c r="Z807" t="inlineStr">
         <is>
           <t>35740</t>
         </is>
@@ -48763,17 +49213,17 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U808" t="inlineStr">
+      <c r="X808" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
       </c>
-      <c r="V808" t="inlineStr">
+      <c r="Y808" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
       </c>
-      <c r="W808" t="inlineStr">
+      <c r="Z808" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -48851,17 +49301,17 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U809" t="inlineStr">
+      <c r="X809" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
       </c>
-      <c r="V809" t="inlineStr">
+      <c r="Y809" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
       </c>
-      <c r="W809" t="inlineStr">
+      <c r="Z809" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -48939,17 +49389,17 @@
           <t>THOMAS Martin</t>
         </is>
       </c>
-      <c r="U810" t="inlineStr">
+      <c r="X810" t="inlineStr">
         <is>
           <t>35401</t>
         </is>
       </c>
-      <c r="V810" t="inlineStr">
+      <c r="Y810" t="inlineStr">
         <is>
           <t>35413</t>
         </is>
       </c>
-      <c r="W810" t="inlineStr">
+      <c r="Z810" t="inlineStr">
         <is>
           <t>35412</t>
         </is>
@@ -49027,12 +49477,12 @@
           <t>HINTON Tyler</t>
         </is>
       </c>
-      <c r="U811" t="inlineStr">
+      <c r="X811" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
       </c>
-      <c r="V811" t="inlineStr">
+      <c r="Y811" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -49110,17 +49560,17 @@
           <t>LENARCIC Jure</t>
         </is>
       </c>
-      <c r="U812" t="inlineStr">
+      <c r="X812" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
       </c>
-      <c r="V812" t="inlineStr">
+      <c r="Y812" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
       </c>
-      <c r="W812" t="inlineStr">
+      <c r="Z812" t="inlineStr">
         <is>
           <t>36259</t>
         </is>
@@ -49198,17 +49648,17 @@
           <t>RAK Tomas</t>
         </is>
       </c>
-      <c r="U813" t="inlineStr">
+      <c r="X813" t="inlineStr">
         <is>
           <t>35059</t>
         </is>
       </c>
-      <c r="V813" t="inlineStr">
+      <c r="Y813" t="inlineStr">
         <is>
           <t>35037</t>
         </is>
       </c>
-      <c r="W813" t="inlineStr">
+      <c r="Z813" t="inlineStr">
         <is>
           <t>35056</t>
         </is>
@@ -49286,17 +49736,17 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U814" t="inlineStr">
+      <c r="X814" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
       </c>
-      <c r="V814" t="inlineStr">
+      <c r="Y814" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
       </c>
-      <c r="W814" t="inlineStr">
+      <c r="Z814" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -49374,17 +49824,17 @@
           <t>VAN DER KNIJFF Annebel</t>
         </is>
       </c>
-      <c r="U815" t="inlineStr">
+      <c r="X815" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
       </c>
-      <c r="V815" t="inlineStr">
+      <c r="Y815" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
       </c>
-      <c r="W815" t="inlineStr">
+      <c r="Z815" t="inlineStr">
         <is>
           <t>39945</t>
         </is>
@@ -49462,17 +49912,17 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U816" t="inlineStr">
+      <c r="X816" t="inlineStr">
         <is>
           <t>35309</t>
         </is>
       </c>
-      <c r="V816" t="inlineStr">
+      <c r="Y816" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
       </c>
-      <c r="W816" t="inlineStr">
+      <c r="Z816" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -49550,12 +50000,12 @@
           <t>BORROWS Alison</t>
         </is>
       </c>
-      <c r="V817" t="inlineStr">
+      <c r="Y817" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
       </c>
-      <c r="W817" t="inlineStr">
+      <c r="Z817" t="inlineStr">
         <is>
           <t>38440</t>
         </is>
@@ -49633,17 +50083,17 @@
           <t>HERZOG Andrea</t>
         </is>
       </c>
-      <c r="U818" t="inlineStr">
+      <c r="X818" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
       </c>
-      <c r="V818" t="inlineStr">
+      <c r="Y818" t="inlineStr">
         <is>
           <t>43464</t>
         </is>
       </c>
-      <c r="W818" t="inlineStr">
+      <c r="Z818" t="inlineStr">
         <is>
           <t>55099</t>
         </is>
@@ -49721,17 +50171,17 @@
           <t>TIXIER Cecile</t>
         </is>
       </c>
-      <c r="U819" t="inlineStr">
+      <c r="X819" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
       </c>
-      <c r="V819" t="inlineStr">
+      <c r="Y819" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
       </c>
-      <c r="W819" t="inlineStr">
+      <c r="Z819" t="inlineStr">
         <is>
           <t>35687</t>
         </is>
@@ -49809,12 +50259,12 @@
           <t>GIBSON Eilidh</t>
         </is>
       </c>
-      <c r="V820" t="inlineStr">
+      <c r="Y820" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
       </c>
-      <c r="W820" t="inlineStr">
+      <c r="Z820" t="inlineStr">
         <is>
           <t>36708</t>
         </is>
@@ -49892,7 +50342,7 @@
           <t>FISEROVA Tereza</t>
         </is>
       </c>
-      <c r="V821" t="inlineStr">
+      <c r="Y821" t="inlineStr">
         <is>
           <t>36015</t>
         </is>
@@ -49970,17 +50420,17 @@
           <t>ZHAO Zhengchao</t>
         </is>
       </c>
-      <c r="U822" t="inlineStr">
+      <c r="X822" t="inlineStr">
         <is>
           <t>52024</t>
         </is>
       </c>
-      <c r="V822" t="inlineStr">
+      <c r="Y822" t="inlineStr">
         <is>
           <t>62343</t>
         </is>
       </c>
-      <c r="W822" t="inlineStr">
+      <c r="Z822" t="inlineStr">
         <is>
           <t>63802</t>
         </is>
@@ -50058,12 +50508,12 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="V823" t="inlineStr">
+      <c r="Y823" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
       </c>
-      <c r="W823" t="inlineStr">
+      <c r="Z823" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -50141,12 +50591,12 @@
           <t>PROZHERIN Artem</t>
         </is>
       </c>
-      <c r="U824" t="inlineStr">
+      <c r="X824" t="inlineStr">
         <is>
           <t>35458</t>
         </is>
       </c>
-      <c r="W824" t="inlineStr">
+      <c r="Z824" t="inlineStr">
         <is>
           <t>35775</t>
         </is>
@@ -50224,17 +50674,17 @@
           <t>RYAN Cade</t>
         </is>
       </c>
-      <c r="U825" t="inlineStr">
+      <c r="X825" t="inlineStr">
         <is>
           <t>36683</t>
         </is>
       </c>
-      <c r="V825" t="inlineStr">
+      <c r="Y825" t="inlineStr">
         <is>
           <t>43077</t>
         </is>
       </c>
-      <c r="W825" t="inlineStr">
+      <c r="Z825" t="inlineStr">
         <is>
           <t>37919</t>
         </is>
@@ -50312,17 +50762,17 @@
           <t>OSCHMAUTZ Felix</t>
         </is>
       </c>
-      <c r="U826" t="inlineStr">
+      <c r="X826" t="inlineStr">
         <is>
           <t>35281</t>
         </is>
       </c>
-      <c r="V826" t="inlineStr">
+      <c r="Y826" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
       </c>
-      <c r="W826" t="inlineStr">
+      <c r="Z826" t="inlineStr">
         <is>
           <t>51856</t>
         </is>
@@ -50400,17 +50850,17 @@
           <t>SNIOKA Justinas</t>
         </is>
       </c>
-      <c r="U827" t="inlineStr">
+      <c r="X827" t="inlineStr">
         <is>
           <t>35619</t>
         </is>
       </c>
-      <c r="V827" t="inlineStr">
+      <c r="Y827" t="inlineStr">
         <is>
           <t>36965</t>
         </is>
       </c>
-      <c r="W827" t="inlineStr">
+      <c r="Z827" t="inlineStr">
         <is>
           <t>42915</t>
         </is>
@@ -50488,17 +50938,17 @@
           <t>LEE Dongheon</t>
         </is>
       </c>
-      <c r="U828" t="inlineStr">
+      <c r="X828" t="inlineStr">
         <is>
           <t>42400</t>
         </is>
       </c>
-      <c r="V828" t="inlineStr">
+      <c r="Y828" t="inlineStr">
         <is>
           <t>42398</t>
         </is>
       </c>
-      <c r="W828" t="inlineStr">
+      <c r="Z828" t="inlineStr">
         <is>
           <t>64855</t>
         </is>
@@ -50576,17 +51026,17 @@
           <t>CHEN Bo-Wun</t>
         </is>
       </c>
-      <c r="U829" t="inlineStr">
+      <c r="X829" t="inlineStr">
         <is>
           <t>39369</t>
         </is>
       </c>
-      <c r="V829" t="inlineStr">
+      <c r="Y829" t="inlineStr">
         <is>
           <t>37001</t>
         </is>
       </c>
-      <c r="W829" t="inlineStr">
+      <c r="Z829" t="inlineStr">
         <is>
           <t>36365</t>
         </is>
@@ -50664,17 +51114,17 @@
           <t>GRIMM Alexander</t>
         </is>
       </c>
-      <c r="U830" t="inlineStr">
+      <c r="X830" t="inlineStr">
         <is>
           <t>35114</t>
         </is>
       </c>
-      <c r="V830" t="inlineStr">
+      <c r="Y830" t="inlineStr">
         <is>
           <t>35115</t>
         </is>
       </c>
-      <c r="W830" t="inlineStr">
+      <c r="Z830" t="inlineStr">
         <is>
           <t>35112</t>
         </is>
@@ -50752,17 +51202,17 @@
           <t>YAZAWA Kazuki</t>
         </is>
       </c>
-      <c r="U831" t="inlineStr">
+      <c r="X831" t="inlineStr">
         <is>
           <t>36646</t>
         </is>
       </c>
-      <c r="V831" t="inlineStr">
+      <c r="Y831" t="inlineStr">
         <is>
           <t>47085</t>
         </is>
       </c>
-      <c r="W831" t="inlineStr">
+      <c r="Z831" t="inlineStr">
         <is>
           <t>36482</t>
         </is>
@@ -50840,12 +51290,12 @@
           <t>MARTINS TAQUES Ricardo</t>
         </is>
       </c>
-      <c r="V832" t="inlineStr">
+      <c r="Y832" t="inlineStr">
         <is>
           <t>38023</t>
         </is>
       </c>
-      <c r="W832" t="inlineStr">
+      <c r="Z832" t="inlineStr">
         <is>
           <t>38022</t>
         </is>
@@ -50923,17 +51373,17 @@
           <t>DOUGOUD Martin</t>
         </is>
       </c>
-      <c r="U833" t="inlineStr">
+      <c r="X833" t="inlineStr">
         <is>
           <t>35346</t>
         </is>
       </c>
-      <c r="V833" t="inlineStr">
+      <c r="Y833" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
       </c>
-      <c r="W833" t="inlineStr">
+      <c r="Z833" t="inlineStr">
         <is>
           <t>35426</t>
         </is>
@@ -51011,17 +51461,17 @@
           <t>NABASKUES Unai</t>
         </is>
       </c>
-      <c r="U834" t="inlineStr">
+      <c r="X834" t="inlineStr">
         <is>
           <t>35749</t>
         </is>
       </c>
-      <c r="V834" t="inlineStr">
+      <c r="Y834" t="inlineStr">
         <is>
           <t>35786</t>
         </is>
       </c>
-      <c r="W834" t="inlineStr">
+      <c r="Z834" t="inlineStr">
         <is>
           <t>38775</t>
         </is>
@@ -51099,17 +51549,17 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U835" t="inlineStr">
+      <c r="X835" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
       </c>
-      <c r="V835" t="inlineStr">
+      <c r="Y835" t="inlineStr">
         <is>
           <t>35088</t>
         </is>
       </c>
-      <c r="W835" t="inlineStr">
+      <c r="Z835" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -51187,17 +51637,17 @@
           <t>MANN Aaron</t>
         </is>
       </c>
-      <c r="U836" t="inlineStr">
+      <c r="X836" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
       </c>
-      <c r="V836" t="inlineStr">
+      <c r="Y836" t="inlineStr">
         <is>
           <t>36444</t>
         </is>
       </c>
-      <c r="W836" t="inlineStr">
+      <c r="Z836" t="inlineStr">
         <is>
           <t>39898</t>
         </is>
@@ -51275,17 +51725,17 @@
           <t>ROSSI Lucas</t>
         </is>
       </c>
-      <c r="U837" t="inlineStr">
+      <c r="X837" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
       </c>
-      <c r="V837" t="inlineStr">
+      <c r="Y837" t="inlineStr">
         <is>
           <t>36918</t>
         </is>
       </c>
-      <c r="W837" t="inlineStr">
+      <c r="Z837" t="inlineStr">
         <is>
           <t>36925</t>
         </is>
@@ -51363,17 +51813,17 @@
           <t>HAYWARD Ben</t>
         </is>
       </c>
-      <c r="U838" t="inlineStr">
+      <c r="X838" t="inlineStr">
         <is>
           <t>36262</t>
         </is>
       </c>
-      <c r="V838" t="inlineStr">
+      <c r="Y838" t="inlineStr">
         <is>
           <t>35540</t>
         </is>
       </c>
-      <c r="W838" t="inlineStr">
+      <c r="Z838" t="inlineStr">
         <is>
           <t>35539</t>
         </is>
@@ -51451,12 +51901,12 @@
           <t>MERRITT Jaxon</t>
         </is>
       </c>
-      <c r="U839" t="inlineStr">
+      <c r="X839" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
       </c>
-      <c r="V839" t="inlineStr">
+      <c r="Y839" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -51534,17 +51984,17 @@
           <t>BRUS Simon</t>
         </is>
       </c>
-      <c r="U840" t="inlineStr">
+      <c r="X840" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
       </c>
-      <c r="V840" t="inlineStr">
+      <c r="Y840" t="inlineStr">
         <is>
           <t>36268</t>
         </is>
       </c>
-      <c r="W840" t="inlineStr">
+      <c r="Z840" t="inlineStr">
         <is>
           <t>39076</t>
         </is>
@@ -51622,17 +52072,17 @@
           <t>DE GENNARO Giovanni</t>
         </is>
       </c>
-      <c r="U841" t="inlineStr">
+      <c r="X841" t="inlineStr">
         <is>
           <t>42017</t>
         </is>
       </c>
-      <c r="V841" t="inlineStr">
+      <c r="Y841" t="inlineStr">
         <is>
           <t>35502</t>
         </is>
       </c>
-      <c r="W841" t="inlineStr">
+      <c r="Z841" t="inlineStr">
         <is>
           <t>35244</t>
         </is>
@@ -51710,17 +52160,17 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U842" t="inlineStr">
+      <c r="X842" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
       </c>
-      <c r="V842" t="inlineStr">
+      <c r="Y842" t="inlineStr">
         <is>
           <t>39246</t>
         </is>
       </c>
-      <c r="W842" t="inlineStr">
+      <c r="Z842" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -51798,12 +52248,12 @@
           <t>FORBES-CRYANS Bradley</t>
         </is>
       </c>
-      <c r="V843" t="inlineStr">
+      <c r="Y843" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
       </c>
-      <c r="W843" t="inlineStr">
+      <c r="Z843" t="inlineStr">
         <is>
           <t>36513</t>
         </is>
@@ -51881,17 +52331,17 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U844" t="inlineStr">
+      <c r="X844" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
       </c>
-      <c r="V844" t="inlineStr">
+      <c r="Y844" t="inlineStr">
         <is>
           <t>35031</t>
         </is>
       </c>
-      <c r="W844" t="inlineStr">
+      <c r="Z844" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -51969,17 +52419,17 @@
           <t>NEVEU Boris</t>
         </is>
       </c>
-      <c r="U845" t="inlineStr">
+      <c r="X845" t="inlineStr">
         <is>
           <t>35484</t>
         </is>
       </c>
-      <c r="V845" t="inlineStr">
+      <c r="Y845" t="inlineStr">
         <is>
           <t>35234</t>
         </is>
       </c>
-      <c r="W845" t="inlineStr">
+      <c r="Z845" t="inlineStr">
         <is>
           <t>35396</t>
         </is>

--- a/events/LeeValley_2015_WCH/LeeValley_2015_WCH_start.xlsx
+++ b/events/LeeValley_2015_WCH/LeeValley_2015_WCH_start.xlsx
@@ -13374,7 +13374,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>LIB</t>
+          <t>LBN</t>
         </is>
       </c>
       <c r="J218" t="n">
@@ -19934,7 +19934,7 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>LIB</t>
+          <t>LBN</t>
         </is>
       </c>
       <c r="J333" t="n">

--- a/events/LeeValley_2015_WCH/LeeValley_2015_WCH_start.xlsx
+++ b/events/LeeValley_2015_WCH/LeeValley_2015_WCH_start.xlsx
@@ -13388,6 +13388,11 @@
           <t>MERJAN Richard</t>
         </is>
       </c>
+      <c r="X218" t="inlineStr">
+        <is>
+          <t>45918</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -19946,6 +19951,11 @@
       <c r="R333" t="inlineStr">
         <is>
           <t>MERJAN Richard</t>
+        </is>
+      </c>
+      <c r="X333" t="inlineStr">
+        <is>
+          <t>45918</t>
         </is>
       </c>
     </row>
